--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>96.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>36.48999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>93.73</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-140.53</t>
+          <t>-132.83</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>13322.2</t>
+          <t>9112.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9983.0</t>
+          <t>10143.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>10864.78</t>
+          <t>10903.52</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>-1031</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-37.96790922841592</t>
+          <t>-5.682391237693427</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>504.99</v>
+        <v>171.89</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,22 +1182,22 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>346.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-38.52</t>
+          <t>-38.69</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.92</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.87</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-148.06</t>
+          <t>-140.53</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>12815.0</t>
+          <t>13322.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9174.3</t>
+          <t>9983.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>10767.54</t>
+          <t>10864.78</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-136.6879882337716</t>
+          <t>-37.96790922841592</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>353.5</v>
+        <v>504.99</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-35.96</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,27 +1613,27 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-40.10</t>
+          <t>-38.52</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,17 +1871,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.94</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-155.16</t>
+          <t>-148.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7790.0</t>
+          <t>10867.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>11225.6</t>
+          <t>12815.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8644.1</t>
+          <t>9174.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>10700.16</t>
+          <t>10767.54</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-225.8129528913312</t>
+          <t>-136.6879882337716</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>328.46</v>
+        <v>353.5</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-35.96</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,17 +2044,17 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>29.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-40.77</t>
+          <t>-40.10</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>92.91</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>34.76000000000001</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>37.14</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-161.01</t>
+          <t>-155.16</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7050.0</t>
+          <t>7790.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>12072.6</t>
+          <t>11225.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8733.0</t>
+          <t>8644.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>10666.92</t>
+          <t>10700.16</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-326.5890303820044</t>
+          <t>-225.8129528913312</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>610.63</v>
+        <v>328.46</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-38.30</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,37 +2475,37 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>782.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-40.02</t>
+          <t>-40.77</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,37 +2733,37 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-7.3</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2773,37 +2773,37 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.76000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.14</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-166.10</t>
+          <t>-161.01</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28133.0</t>
+          <t>7050.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>11174.8</t>
+          <t>12072.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8692.0</t>
+          <t>8733.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>10726.62</t>
+          <t>10666.92</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-496.9918671805608</t>
+          <t>-326.5890303820044</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>1071.21</v>
+        <v>610.63</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-37.52</t>
+          <t>-38.30</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,37 +2906,37 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>782.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-43.93</t>
+          <t>-40.02</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-170.40</t>
+          <t>-166.10</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10235.0</t>
+          <t>28133.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>6643.8</t>
+          <t>11174.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>6655.2</t>
+          <t>8692.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10442.72</t>
+          <t>10726.62</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-782.1187092158507</t>
+          <t>-496.9918671805608</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-567.97</v>
+        <v>1071.21</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-41.59</t>
+          <t>-37.52</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,37 +3337,37 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.69</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-42.68</t>
+          <t>-43.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,262 +3595,262 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>34.18</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>34.51</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>37.35</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>39.94</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-170.40</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>30753.61777456647</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>10235.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>6643.8</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>6655.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>10442.72</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-782.1187092158507</t>
+        </is>
+      </c>
+      <c r="BC8" t="n">
+        <v>-567.97</v>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>2025/02/07</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-41.59</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>森鉅</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>森鉅</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>1.208426324097763</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-59.47383334423156</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-7.443059494677986</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>9.45</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>11.23</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>17.82%</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>-12.45%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>49.03</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>7367</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>複合板73.54%、其他26.46% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>森鉅-其他-上櫃</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>其他右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
           <t>34.35</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>34.64</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>37.49</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>40.08</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-172.60</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>30782.74602026049</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>2920.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>5533.6</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>6266.4</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>10337.92</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-732</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-821.0540804272034</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-971.73</v>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>2025/02/07</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-40.29</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>森鉅</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>森鉅</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>-33.03995869213985</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-33.27114283343016</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>4.711714977007549</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>11.2</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>17.82%</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>-12.45%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>138.61</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>7347</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>複合板73.54%、其他26.46% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>森鉅-其他-上櫃</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>其他右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>34.2</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
           <t>34.45</t>
@@ -3858,12 +3858,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>354.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-18.47</t>
+          <t>-11.69</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-43.43</t>
+          <t>-42.68</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,37 +4026,37 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -4066,37 +4066,37 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>37.49</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>40.22</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-175.32</t>
+          <t>-172.60</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>12025.0</t>
+          <t>2920.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6062.6</t>
+          <t>5533.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>7436.1</t>
+          <t>6266.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>10449.0</t>
+          <t>10337.92</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1373</t>
+          <t>-732</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-793.6580704618908</t>
+          <t>-821.0540804272034</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-730.0700000000001</v>
+        <v>-971.73</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-41.07</t>
+          <t>-40.29</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>354.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-18.47</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-42.60</t>
+          <t>-43.43</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>34.42</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>34.75</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>40.22</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-177.68</t>
+          <t>-175.32</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2561.0</t>
+          <t>12025.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5393.4</t>
+          <t>6062.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6995.1</t>
+          <t>7436.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>10355.28</t>
+          <t>10449.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1601</t>
+          <t>-1373</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-805.2187173075337</t>
+          <t>-793.6580704618908</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-1334.31</v>
+        <v>-730.0700000000001</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-41.07</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,37 +4630,37 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>6.88</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.55</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-43.01</t>
+          <t>-42.60</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,37 +4888,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,37 +4928,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>34.42</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.36</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-180.27</t>
+          <t>-177.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5478.0</t>
+          <t>2561.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6209.2</t>
+          <t>5393.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7352.5</t>
+          <t>6995.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>10615.86</t>
+          <t>10355.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1143</t>
+          <t>-1601</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-709.020127279875</t>
+          <t>-805.2187173075337</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1135.85</v>
+        <v>-1334.31</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-40.64</t>
+          <t>-40.21</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>34.55</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-8.57</t>
+          <t>-15.55</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-42.51</t>
+          <t>-43.01</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-2.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>192</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-7.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-6.41</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.44</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>35.15</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>11.04</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-182.48</t>
+          <t>-180.27</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30782.74602026049</t>
+          <t>30753.61777456647</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4684.0</t>
+          <t>5478.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6666.6</t>
+          <t>6209.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7291.4</t>
+          <t>7352.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>11029.14</t>
+          <t>10615.86</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-624</t>
+          <t>-1143</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-631.4143454063285</t>
+          <t>-709.020127279875</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1124.31</v>
+        <v>-1135.85</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-40.12</t>
+          <t>-40.64</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-33.03995869213985</t>
+          <t>1.208426324097763</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-33.27114283343016</t>
+          <t>-59.47383334423156</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>4.711714977007549</t>
+          <t>-7.443059494677986</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.45</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>11.23</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>138.61</t>
+          <t>49.03</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>34.25</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>34.55</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1899.74</t>
+          <t>1070.149</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
           <t>59.09</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>86.36</t>
-        </is>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-104.55</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>53103106.4</t>
+          <t>56141296.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>30684373.7</t>
+          <t>31853386.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>31832273.68</t>
+          <t>31581240.88</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>22418732</t>
+          <t>24287909</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>94710.08996855281</t>
+          <t>760783.064382198</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>7015851.23</v>
+        <v>4424184.42</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5923,37 +5923,37 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4856.308</t>
+          <t>1899.74</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.95</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>73.06</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>80.63</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-105.46</t>
+          <t>-104.55</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>46491657.4</t>
+          <t>53103106.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>28068835.8</t>
+          <t>30684373.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>31715644.28</t>
+          <t>31832273.68</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>18422821</t>
+          <t>22418732</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-1163679.207782453</t>
+          <t>94710.08996855281</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>8618125.01</v>
+        <v>7015851.23</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6354,37 +6354,37 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5394.844</t>
+          <t>4856.308</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>65.63</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,37 +6627,37 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -6667,22 +6667,22 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-106.42</t>
+          <t>-105.46</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>105971815.0</t>
+          <t>98186083.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28561653.4</t>
+          <t>46491657.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>20582217.5</t>
+          <t>28068835.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>30693683.24</t>
+          <t>31715644.28</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>7979435</t>
+          <t>18422821</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-2942189.06570945</t>
+          <t>-1163679.207782453</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>4067675.63</v>
+        <v>8618125.01</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6785,37 +6785,37 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1052.024</t>
+          <t>5394.844</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>-8.52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-22.06</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.42</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>19362408.0</t>
+          <t>105971815.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>8931432.4</t>
+          <t>28561653.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>11459635.1</t>
+          <t>20582217.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>29700594.34</t>
+          <t>30693683.24</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2528202</t>
+          <t>7979435</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-4216709.919349549</t>
+          <t>-2942189.06570945</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-3412426.05</v>
+        <v>4067675.63</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7216,17 +7216,17 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
@@ -7236,17 +7236,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>269.064</t>
+          <t>1052.024</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-30.08</t>
+          <t>-22.06</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-45.72</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.43</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4770946.0</t>
+          <t>19362408.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>7565476.8</t>
+          <t>8931432.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10819850.9</t>
+          <t>11459635.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>32149291.2</t>
+          <t>29700594.34</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3254374</t>
+          <t>-2528202</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-4362943.35099234</t>
+          <t>-4216709.919349549</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-4696833.9</v>
+        <v>-3412426.05</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7647,37 +7647,37 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>17.55</t>
-        </is>
-      </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>232.654</t>
+          <t>269.064</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-30.08</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-54.39</t>
+          <t>-45.72</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-105.69</t>
+          <t>-106.43</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4167035.0</t>
+          <t>4770946.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8265641.0</t>
+          <t>7565476.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>11626271.8</t>
+          <t>10819850.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>36405486.04</t>
+          <t>32149291.2</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-3360630</t>
+          <t>-3254374</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4302235.978390328</t>
+          <t>-4362943.35099234</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-4800587.27</v>
+        <v>-4696833.9</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8078,22 +8078,22 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,17 +8158,17 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>472.584</t>
+          <t>232.654</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,17 +8336,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>18.19</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-61.11</t>
+          <t>-54.39</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.92</t>
+          <t>-105.69</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>8536063.0</t>
+          <t>4167035.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>9646014.2</t>
+          <t>8265641.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>12277720.6</t>
+          <t>11626271.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>36739025.16</t>
+          <t>36405486.04</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2631706</t>
+          <t>-3360630</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4211626.652982336</t>
+          <t>-4302235.978390328</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-4712652.07</v>
+        <v>-4800587.27</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8509,22 +8509,22 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>440.246</t>
+          <t>472.584</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-3.96</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
           <t>-2.08</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-4.23</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>18.19</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-61.11</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.17</t>
+          <t>-104.92</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7820710.0</t>
+          <t>8536063.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>12602781.6</t>
+          <t>9646014.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>13462201.6</t>
+          <t>12277720.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>37163238.48</t>
+          <t>36739025.16</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-859420</t>
+          <t>-2631706</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4120531.122661845</t>
+          <t>-4211626.652982336</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-4886831.5</v>
+        <v>-4712652.07</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8940,17 +8940,17 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>689.656</t>
+          <t>440.246</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>6.28</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.23</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-90.71</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.17</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>12532630.0</t>
+          <t>7820710.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>13987837.8</t>
+          <t>12602781.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>14092302.0</t>
+          <t>13462201.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>37776316.58</t>
+          <t>37163238.48</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-104464</t>
+          <t>-859420</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-3981203.781668247</t>
+          <t>-4120531.122661845</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-4884484.59</v>
+        <v>-4886831.5</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>445.754</t>
+          <t>689.656</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.47</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-83.66</t>
+          <t>-90.71</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-102.56</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>8271767.0</t>
+          <t>12532630.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>14074225.0</t>
+          <t>13987837.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13955521.7</t>
+          <t>14092302.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>38595032.04</t>
+          <t>37776316.58</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>118703</t>
+          <t>-104464</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-3816970.907006088</t>
+          <t>-3981203.781668247</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-5211534.56</v>
+        <v>-4884484.59</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9802,22 +9802,22 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>596.858</t>
+          <t>445.754</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.64</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>19.13</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>19.47</t>
+          <t>19.43</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-128.37</t>
+          <t>-83.66</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-102.02</t>
+          <t>-102.56</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>69419985.87698987</t>
+          <t>69362937.98193641</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>11068901.0</t>
+          <t>8271767.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>14986902.6</t>
+          <t>14074225.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14295731.4</t>
+          <t>13955521.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>40984558.32</t>
+          <t>38595032.04</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>691171</t>
+          <t>118703</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3563413.878671399</t>
+          <t>-3816970.907006088</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-5036101.54</v>
+        <v>-5211534.56</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10233,22 +10233,22 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-1.138608992641734</t>
+          <t>4.154975628533399</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>19.71039597260941</t>
+          <t>16.21035637221673</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>3.946022481366093</t>
+          <t>6.111603549217973</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>112.35</t>
+          <t>107.06</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>146.36</t>
+          <t>142.7</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>18.35</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-39.10</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>36.48999999999999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>36.71</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>108.68</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-132.83</t>
+          <t>-125.82</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>9112.4</t>
+          <t>10646.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>10143.6</t>
+          <t>11359.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>10903.52</t>
+          <t>10960.76</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1031</t>
+          <t>-713</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5.682391237693427</t>
+          <t>73.2099091766697</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>171.89</v>
+        <v>507.12</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-36.57</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>96.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>36.48999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>93.73</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-140.53</t>
+          <t>-132.83</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13322.2</t>
+          <t>9112.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9983.0</t>
+          <t>10143.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>10864.78</t>
+          <t>10903.52</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>-1031</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-37.96790922841592</t>
+          <t>-5.682391237693427</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>504.99</v>
+        <v>171.89</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>346.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-38.52</t>
+          <t>-38.69</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.92</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.87</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-148.06</t>
+          <t>-140.53</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>12815.0</t>
+          <t>13322.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>9174.3</t>
+          <t>9983.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>10767.54</t>
+          <t>10864.78</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-136.6879882337716</t>
+          <t>-37.96790922841592</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>353.5</v>
+        <v>504.99</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-35.96</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-40.10</t>
+          <t>-38.52</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.94</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-155.16</t>
+          <t>-148.06</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>7790.0</t>
+          <t>10867.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>11225.6</t>
+          <t>12815.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8644.1</t>
+          <t>9174.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>10700.16</t>
+          <t>10767.54</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-225.8129528913312</t>
+          <t>-136.6879882337716</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>328.46</v>
+        <v>353.5</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-35.96</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>29.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-40.77</t>
+          <t>-40.10</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>92.91</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>34.76000000000001</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>37.14</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-161.01</t>
+          <t>-155.16</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7050.0</t>
+          <t>7790.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>12072.6</t>
+          <t>11225.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8733.0</t>
+          <t>8644.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>10666.92</t>
+          <t>10700.16</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-326.5890303820044</t>
+          <t>-225.8129528913312</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>610.63</v>
+        <v>328.46</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-38.30</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>782.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-40.02</t>
+          <t>-40.77</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,37 +3164,37 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-7.3</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -3204,37 +3204,37 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.76000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-166.10</t>
+          <t>-161.01</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>28133.0</t>
+          <t>7050.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>11174.8</t>
+          <t>12072.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8692.0</t>
+          <t>8733.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10726.62</t>
+          <t>10666.92</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-496.9918671805608</t>
+          <t>-326.5890303820044</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>1071.21</v>
+        <v>610.63</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-37.52</t>
+          <t>-38.30</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>782.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.04</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-43.93</t>
+          <t>-40.02</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-170.40</t>
+          <t>-166.10</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10235.0</t>
+          <t>28133.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>6643.8</t>
+          <t>11174.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6655.2</t>
+          <t>8692.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10442.72</t>
+          <t>10726.62</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-782.1187092158507</t>
+          <t>-496.9918671805608</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-567.97</v>
+        <v>1071.21</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-41.59</t>
+          <t>-37.52</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.69</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-42.68</t>
+          <t>-43.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,262 +4026,262 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>34.18</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>34.51</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>37.35</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>39.94</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-170.40</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>30741.10173160173</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>10235.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>6643.8</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>6655.2</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>10442.72</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-782.1187092158507</t>
+        </is>
+      </c>
+      <c r="BC9" t="n">
+        <v>-567.97</v>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>2025/02/07</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-41.59</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>森鉅</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>森鉅</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>1.208426324097763</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-59.47383334423156</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-7.443059494677986</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>9.56</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>11.09</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>17.82%</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>-12.45%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>48.68</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>7278</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>複合板73.54%、其他26.46% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>森鉅-其他-上櫃</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>其他右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
           <t>34.35</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>34.64</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>37.49</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>40.08</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-172.60</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>30753.61777456647</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2920.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>5533.6</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>6266.4</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>10337.92</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-732</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-821.0540804272034</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-971.73</v>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>2025/02/07</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-40.29</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>森鉅</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>森鉅</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>1.208426324097763</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-59.47383334423156</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-7.443059494677986</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>9.45</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>11.23</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>17.82%</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>-12.45%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>49.03</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>7367</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>複合板73.54%、其他26.46% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>森鉅-其他-上櫃</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>其他右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>34.2</t>
-        </is>
-      </c>
       <c r="CD9" t="inlineStr">
         <is>
           <t>34.45</t>
@@ -4289,12 +4289,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>354.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-18.47</t>
+          <t>-11.69</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-43.43</t>
+          <t>-42.68</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,37 +4457,37 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -4497,37 +4497,37 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>37.49</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>40.22</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-175.32</t>
+          <t>-172.60</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>12025.0</t>
+          <t>2920.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>6062.6</t>
+          <t>5533.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7436.1</t>
+          <t>6266.4</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>10449.0</t>
+          <t>10337.92</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1373</t>
+          <t>-732</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-793.6580704618908</t>
+          <t>-821.0540804272034</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-730.0700000000001</v>
+        <v>-971.73</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-41.07</t>
+          <t>-40.29</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>354.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-18.47</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-42.60</t>
+          <t>-43.43</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>34.42</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>34.75</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>40.22</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-177.68</t>
+          <t>-175.32</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2561.0</t>
+          <t>12025.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5393.4</t>
+          <t>6062.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6995.1</t>
+          <t>7436.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>10355.28</t>
+          <t>10449.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1601</t>
+          <t>-1373</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-805.2187173075337</t>
+          <t>-793.6580704618908</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-1334.31</v>
+        <v>-730.0700000000001</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-41.07</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.55</t>
+          <t>-22.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-43.01</t>
+          <t>-42.60</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.77</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,37 +5319,37 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>398</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>31.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-7.54</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5359,37 +5359,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>34.44</t>
+          <t>34.42</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>40.36</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-180.27</t>
+          <t>-177.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30753.61777456647</t>
+          <t>30741.10173160173</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5478.0</t>
+          <t>2561.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6209.2</t>
+          <t>5393.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7352.5</t>
+          <t>6995.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>10615.86</t>
+          <t>10355.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1143</t>
+          <t>-1601</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-709.020127279875</t>
+          <t>-805.2187173075337</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1135.85</v>
+        <v>-1334.31</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-40.64</t>
+          <t>-40.21</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.45</t>
+          <t>9.56</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>11.23</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>49.03</t>
+          <t>48.68</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7278</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>34.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>34.25</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1070.149</t>
+          <t>1035.185</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,72 +5750,72 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.10</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>56141296.2</t>
+          <t>55940470.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31853386.5</t>
+          <t>32435951.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>31581240.88</t>
+          <t>31266005.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>24287909</t>
+          <t>23504518</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>760783.064382198</t>
+          <t>1009761.316062864</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>4424184.42</v>
+        <v>2379141.7</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1899.74</t>
+          <t>1070.149</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.95</t>
+          <t>-3.7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,77 +6181,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
           <t>59.09</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>86.36</t>
-        </is>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-104.55</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>53103106.4</t>
+          <t>56141296.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>30684373.7</t>
+          <t>31853386.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>31832273.68</t>
+          <t>31581240.88</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>22418732</t>
+          <t>24287909</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>94710.08996855281</t>
+          <t>760783.064382198</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>7015851.23</v>
+        <v>4424184.42</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4856.308</t>
+          <t>1899.74</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-9.89</t>
+          <t>-8.83</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>73.06</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>80.63</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-105.46</t>
+          <t>-104.55</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>46491657.4</t>
+          <t>53103106.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28068835.8</t>
+          <t>30684373.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31715644.28</t>
+          <t>31832273.68</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>18422821</t>
+          <t>22418732</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1163679.207782453</t>
+          <t>94710.08996855281</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>8618125.01</v>
+        <v>7015851.23</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5394.844</t>
+          <t>4856.308</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-8.52</t>
+          <t>-13.96</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>65.63</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,37 +7058,37 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -7098,22 +7098,22 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-106.42</t>
+          <t>-105.46</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>105971815.0</t>
+          <t>98186083.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28561653.4</t>
+          <t>46491657.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>20582217.5</t>
+          <t>28068835.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>30693683.24</t>
+          <t>31715644.28</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7979435</t>
+          <t>18422821</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-2942189.06570945</t>
+          <t>-1163679.207782453</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>4067675.63</v>
+        <v>8618125.01</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1052.024</t>
+          <t>5394.844</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-12.54</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-22.06</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.42</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>19362408.0</t>
+          <t>105971815.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>8931432.4</t>
+          <t>28561653.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>11459635.1</t>
+          <t>20582217.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>29700594.34</t>
+          <t>30693683.24</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2528202</t>
+          <t>7979435</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-4216709.919349549</t>
+          <t>-2942189.06570945</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-3412426.05</v>
+        <v>4067675.63</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>269.064</t>
+          <t>1052.024</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-5.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-30.08</t>
+          <t>-22.06</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-45.72</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.43</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4770946.0</t>
+          <t>19362408.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>7565476.8</t>
+          <t>8931432.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>10819850.9</t>
+          <t>11459635.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>32149291.2</t>
+          <t>29700594.34</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-3254374</t>
+          <t>-2528202</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4362943.35099234</t>
+          <t>-4216709.919349549</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-4696833.9</v>
+        <v>-3412426.05</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>17.55</t>
-        </is>
-      </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>232.654</t>
+          <t>269.064</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-30.08</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-54.39</t>
+          <t>-45.72</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-105.69</t>
+          <t>-106.43</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4167035.0</t>
+          <t>4770946.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>8265641.0</t>
+          <t>7565476.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>11626271.8</t>
+          <t>10819850.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>36405486.04</t>
+          <t>32149291.2</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-3360630</t>
+          <t>-3254374</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4302235.978390328</t>
+          <t>-4362943.35099234</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-4800587.27</v>
+        <v>-4696833.9</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>472.584</t>
+          <t>232.654</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,17 +8767,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>18.19</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-61.11</t>
+          <t>-54.39</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.92</t>
+          <t>-105.69</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>8536063.0</t>
+          <t>4167035.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>9646014.2</t>
+          <t>8265641.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>12277720.6</t>
+          <t>11626271.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>36739025.16</t>
+          <t>36405486.04</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2631706</t>
+          <t>-3360630</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4211626.652982336</t>
+          <t>-4302235.978390328</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-4712652.07</v>
+        <v>-4800587.27</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>440.246</t>
+          <t>472.584</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-3.96</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
           <t>-2.08</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-4.23</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>18.19</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-61.11</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.17</t>
+          <t>-104.92</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>7820710.0</t>
+          <t>8536063.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>12602781.6</t>
+          <t>9646014.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>13462201.6</t>
+          <t>12277720.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>37163238.48</t>
+          <t>36739025.16</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-859420</t>
+          <t>-2631706</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-4120531.122661845</t>
+          <t>-4211626.652982336</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-4886831.5</v>
+        <v>-4712652.07</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>689.656</t>
+          <t>440.246</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.23</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-90.71</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.17</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>12532630.0</t>
+          <t>7820710.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>13987837.8</t>
+          <t>12602781.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>14092302.0</t>
+          <t>13462201.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>37776316.58</t>
+          <t>37163238.48</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-104464</t>
+          <t>-859420</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-3981203.781668247</t>
+          <t>-4120531.122661845</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-4884484.59</v>
+        <v>-4886831.5</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>445.754</t>
+          <t>689.656</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-4.75</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,17 +10060,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>18.64</t>
+          <t>18.42</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>19.08</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>19.43</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>18.47</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-83.66</t>
+          <t>-90.71</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-102.56</t>
+          <t>-103.31</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>69362937.98193641</t>
+          <t>69302583.69264069</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8271767.0</t>
+          <t>12532630.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>14074225.0</t>
+          <t>13987837.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>13955521.7</t>
+          <t>14092302.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>38595032.04</t>
+          <t>37776316.58</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>118703</t>
+          <t>-104464</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3816970.907006088</t>
+          <t>-3981203.781668247</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-5211534.56</v>
+        <v>-4884484.59</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>107.06</t>
+          <t>103.24</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>142.7</t>
+          <t>138.21</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-39.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.52</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>142.57</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-125.82</t>
+          <t>-119.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>10646.4</t>
+          <t>10351.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11359.5</t>
+          <t>10788.6</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>10960.76</t>
+          <t>10931.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-713</t>
+          <t>-437</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>73.2099091766697</t>
+          <t>77.1468993095428</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>507.12</v>
+        <v>98.8</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-39.10</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>36.48999999999999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>36.71</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>108.68</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-132.83</t>
+          <t>-125.82</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>9112.4</t>
+          <t>10646.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>10143.6</t>
+          <t>11359.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>10903.52</t>
+          <t>10960.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1031</t>
+          <t>-713</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5.682391237693427</t>
+          <t>73.2099091766697</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>171.89</v>
+        <v>507.12</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-36.57</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>96.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>36.48999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>93.73</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-140.53</t>
+          <t>-132.83</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>13322.2</t>
+          <t>9112.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>9983.0</t>
+          <t>10143.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>10864.78</t>
+          <t>10903.52</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>-1031</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-37.96790922841592</t>
+          <t>-5.682391237693427</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>504.99</v>
+        <v>171.89</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>346.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-38.52</t>
+          <t>-38.69</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.92</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.87</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-148.06</t>
+          <t>-140.53</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>12815.0</t>
+          <t>13322.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>9174.3</t>
+          <t>9983.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>10767.54</t>
+          <t>10864.78</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-136.6879882337716</t>
+          <t>-37.96790922841592</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>353.5</v>
+        <v>504.99</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-35.96</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-40.10</t>
+          <t>-38.52</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,17 +2733,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.94</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-155.16</t>
+          <t>-148.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7790.0</t>
+          <t>10867.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>11225.6</t>
+          <t>12815.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8644.1</t>
+          <t>9174.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>10700.16</t>
+          <t>10767.54</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-225.8129528913312</t>
+          <t>-136.6879882337716</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>328.46</v>
+        <v>353.5</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-35.96</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2926,17 +2926,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>29.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-40.77</t>
+          <t>-40.10</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>92.91</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>34.76000000000001</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>37.14</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-161.01</t>
+          <t>-155.16</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7050.0</t>
+          <t>7790.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>12072.6</t>
+          <t>11225.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8733.0</t>
+          <t>8644.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10666.92</t>
+          <t>10700.16</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-326.5890303820044</t>
+          <t>-225.8129528913312</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>610.63</v>
+        <v>328.46</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-38.30</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>782.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-40.02</t>
+          <t>-40.77</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,37 +3595,37 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-7.3</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -3635,37 +3635,37 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.76000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-166.10</t>
+          <t>-161.01</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28133.0</t>
+          <t>7050.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>11174.8</t>
+          <t>12072.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>8692.0</t>
+          <t>8733.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10726.62</t>
+          <t>10666.92</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-496.9918671805608</t>
+          <t>-326.5890303820044</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>1071.21</v>
+        <v>610.63</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-37.52</t>
+          <t>-38.30</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>782.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-43.93</t>
+          <t>-40.02</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-170.40</t>
+          <t>-166.10</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10235.0</t>
+          <t>28133.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>6643.8</t>
+          <t>11174.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6655.2</t>
+          <t>8692.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>10442.72</t>
+          <t>10726.62</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-782.1187092158507</t>
+          <t>-496.9918671805608</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-567.97</v>
+        <v>1071.21</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-41.59</t>
+          <t>-37.52</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>9.16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-11.69</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-42.68</t>
+          <t>-43.93</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,262 +4457,262 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.59</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>34.18</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>34.51</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>37.35</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>39.94</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>12.55</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.98</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-170.40</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/27</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>30710.45749279539</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>10235.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>6643.8</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>6655.2</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>10442.72</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-11</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-782.1187092158507</t>
+        </is>
+      </c>
+      <c r="BC10" t="n">
+        <v>-567.97</v>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>2025/02/07</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>-41.59</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>森鉅</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>森鉅</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>其他</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>1.208426324097763</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-59.47383334423156</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-7.443059494677986</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>9.43</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>11.24</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>17.82%</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>-12.45%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>48.31</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>7377</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>複合板73.54%、其他26.46% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>森鉅-其他-上櫃</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>其他右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
           <t>34.35</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>34.64</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>37.49</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>40.08</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>14.96</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.98</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.58</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-172.60</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>30741.10173160173</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>2920.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>5533.6</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>6266.4</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>10337.92</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-732</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-821.0540804272034</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-971.73</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>57.7</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/02/07</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>-40.29</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>森鉅</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>森鉅</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.7</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>1.208426324097763</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-59.47383334423156</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-7.443059494677986</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>9.56</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>11.09</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>17.82%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>-12.45%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>48.68</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>7278</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>複合板73.54%、其他26.46% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>森鉅-其他-上櫃</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>其他右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>34.2</t>
-        </is>
-      </c>
       <c r="CD10" t="inlineStr">
         <is>
           <t>34.45</t>
@@ -4720,12 +4720,12 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>34.2</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>354.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-18.47</t>
+          <t>-11.69</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-43.43</t>
+          <t>-42.68</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,37 +4888,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>64.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.64</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4928,37 +4928,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>37.62</t>
+          <t>37.49</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>40.22</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>14.96</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-175.32</t>
+          <t>-172.60</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12025.0</t>
+          <t>2920.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>6062.6</t>
+          <t>5533.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7436.1</t>
+          <t>6266.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>10449.0</t>
+          <t>10337.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1373</t>
+          <t>-732</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-793.6580704618908</t>
+          <t>-821.0540804272034</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-730.0700000000001</v>
+        <v>-971.73</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-41.07</t>
+          <t>-40.29</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>34.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>354.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.90</t>
+          <t>-18.47</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-42.60</t>
+          <t>-43.43</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>171</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>31.11</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.54</t>
+          <t>-7.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.41</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>34.42</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>34.75</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>37.62</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>40.22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-177.68</t>
+          <t>-175.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30741.10173160173</t>
+          <t>30710.45749279539</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2561.0</t>
+          <t>12025.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5393.4</t>
+          <t>6062.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6995.1</t>
+          <t>7436.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>10355.28</t>
+          <t>10449.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1601</t>
+          <t>-1373</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-805.2187173075337</t>
+          <t>-793.6580704618908</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-1334.31</v>
+        <v>-730.0700000000001</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-40.21</t>
+          <t>-41.07</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.56</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>48.68</t>
+          <t>48.31</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>34.65</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>34.25</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1035.185</t>
+          <t>507.54</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-38.61</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-104.10</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>55940470.0</t>
+          <t>36519367.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>32435951.2</t>
+          <t>32540510.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>31266005.0</t>
+          <t>30733036.4</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>23504518</t>
+          <t>3978856</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>1009761.316062864</t>
+          <t>881526.5061229398</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>2379141.7</v>
+        <v>176235.05</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1070.149</t>
+          <t>1035.185</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,72 +6181,72 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.10</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>56141296.2</t>
+          <t>55940470.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>31853386.5</t>
+          <t>32435951.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>31581240.88</t>
+          <t>31266005.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>24287909</t>
+          <t>23504518</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>760783.064382198</t>
+          <t>1009761.316062864</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>4424184.42</v>
+        <v>2379141.7</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,42 +6481,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>-4.65</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1070.149</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>18.2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>-4.6</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1899.74</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-8.83</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
           <t>59.09</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>86.36</t>
-        </is>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-104.55</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>53103106.4</t>
+          <t>56141296.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>30684373.7</t>
+          <t>31853386.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>31832273.68</t>
+          <t>31581240.88</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>22418732</t>
+          <t>24287909</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>94710.08996855281</t>
+          <t>760783.064382198</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>7015851.23</v>
+        <v>4424184.42</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4856.308</t>
+          <t>1899.74</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-13.96</t>
+          <t>-9.77</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>73.06</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>12.31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>80.63</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-105.46</t>
+          <t>-104.55</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>46491657.4</t>
+          <t>53103106.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>28068835.8</t>
+          <t>30684373.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31715644.28</t>
+          <t>31832273.68</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>18422821</t>
+          <t>22418732</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-1163679.207782453</t>
+          <t>94710.08996855281</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>8618125.01</v>
+        <v>7015851.23</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>5394.844</t>
+          <t>4856.308</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-12.54</t>
+          <t>-14.94</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>65.63</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>31.46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,37 +7489,37 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -7529,22 +7529,22 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.42</t>
+          <t>-105.46</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>105971815.0</t>
+          <t>98186083.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>28561653.4</t>
+          <t>46491657.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>20582217.5</t>
+          <t>28068835.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>30693683.24</t>
+          <t>31715644.28</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7979435</t>
+          <t>18422821</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-2942189.06570945</t>
+          <t>-1163679.207782453</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>4067675.63</v>
+        <v>8618125.01</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1052.024</t>
+          <t>5394.844</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.41</t>
+          <t>-13.51</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-22.06</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.42</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>19362408.0</t>
+          <t>105971815.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>8931432.4</t>
+          <t>28561653.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>11459635.1</t>
+          <t>20582217.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>29700594.34</t>
+          <t>30693683.24</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2528202</t>
+          <t>7979435</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4216709.919349549</t>
+          <t>-2942189.06570945</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-3412426.05</v>
+        <v>4067675.63</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8098,17 +8098,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>269.064</t>
+          <t>1052.024</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-30.08</t>
+          <t>-22.06</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-45.72</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.43</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4770946.0</t>
+          <t>19362408.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>7565476.8</t>
+          <t>8931432.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>10819850.9</t>
+          <t>11459635.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>32149291.2</t>
+          <t>29700594.34</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-3254374</t>
+          <t>-2528202</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4362943.35099234</t>
+          <t>-4216709.919349549</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-4696833.9</v>
+        <v>-3412426.05</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>17.55</t>
-        </is>
-      </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>232.654</t>
+          <t>269.064</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-30.08</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-54.39</t>
+          <t>-45.72</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-105.69</t>
+          <t>-106.43</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>4167035.0</t>
+          <t>4770946.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>8265641.0</t>
+          <t>7565476.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>11626271.8</t>
+          <t>10819850.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>36405486.04</t>
+          <t>32149291.2</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-3360630</t>
+          <t>-3254374</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4302235.978390328</t>
+          <t>-4362943.35099234</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-4800587.27</v>
+        <v>-4696833.9</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,17 +9020,17 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>472.584</t>
+          <t>232.654</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-21.43</t>
+          <t>-28.91</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.96</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.38</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>18.19</t>
+          <t>18.08</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>19.31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.54</t>
+          <t>18.56</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-61.11</t>
+          <t>-54.39</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.92</t>
+          <t>-105.69</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>8536063.0</t>
+          <t>4167035.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>9646014.2</t>
+          <t>8265641.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>12277720.6</t>
+          <t>11626271.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>36739025.16</t>
+          <t>36405486.04</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2631706</t>
+          <t>-3360630</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-4211626.652982336</t>
+          <t>-4302235.978390328</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-4712652.07</v>
+        <v>-4800587.27</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.25</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>440.246</t>
+          <t>472.584</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-21.43</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
+          <t>-0.22</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-3.96</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
           <t>-2.08</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-4.23</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>-1.69</t>
-        </is>
-      </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>18.23</t>
+          <t>18.19</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>19.34</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>18.54</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-82.40</t>
+          <t>-61.11</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-104.17</t>
+          <t>-104.92</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>7820710.0</t>
+          <t>8536063.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>12602781.6</t>
+          <t>9646014.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>13462201.6</t>
+          <t>12277720.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>37163238.48</t>
+          <t>36739025.16</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-859420</t>
+          <t>-2631706</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4120531.122661845</t>
+          <t>-4211626.652982336</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-4886831.5</v>
+        <v>-4712652.07</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>12.38</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>689.656</t>
+          <t>440.246</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-4.75</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>508</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10080,57 +10080,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>18.42</t>
+          <t>18.23</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>19.08</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>19.36</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.47</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-90.71</t>
+          <t>-82.40</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-103.31</t>
+          <t>-104.17</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>69302583.69264069</t>
+          <t>69221887.53674352</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>12532630.0</t>
+          <t>7820710.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>13987837.8</t>
+          <t>12602781.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>14092302.0</t>
+          <t>13462201.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>37776316.58</t>
+          <t>37163238.48</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-104464</t>
+          <t>-859420</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-3981203.781668247</t>
+          <t>-4120531.122661845</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-4884484.59</v>
+        <v>-4886831.5</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>103.24</t>
+          <t>102.35</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>138.21</t>
+          <t>139.14</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>77.87</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.64</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>365.87</t>
+          <t>2018.96</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>11052.4</t>
+          <t>10871.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>10895.12</t>
+          <t>10687.76</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>11445</v>
+        <v>6181</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-36.22</t>
+          <t>-35.36</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>95.52</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>36.59</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>229.08</t>
+          <t>365.87</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>11317.6</t>
+          <t>11052.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>11140.44</t>
+          <t>10895.12</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>15697</v>
+        <v>11445</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-34.66</t>
+          <t>-36.22</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,12 +1886,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.59</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>142.57</t>
+          <t>229.08</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-119.03</t>
+          <t>-112.10</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>10351.6</t>
+          <t>11317.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>10788.6</t>
+          <t>12066.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>10931.74</t>
+          <t>11140.44</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-437</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>77.1468993095428</t>
+          <t>144.367881711707</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>98.80034504034484</t>
+          <t>514.0832849236103</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>6316</v>
+        <v>15697</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-34.66</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-39.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.52</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>142.57</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-125.82</t>
+          <t>-119.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>10646.4</t>
+          <t>10351.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>11359.5</t>
+          <t>10788.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>10960.76</t>
+          <t>10931.74</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-713</t>
+          <t>-437</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>73.2099091766697</t>
+          <t>77.1468993095428</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>507.1175614556669</t>
+          <t>98.80034504034484</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>14720</v>
+        <v>6316</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-39.10</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>36.48999999999999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>36.71</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>108.68</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-132.83</t>
+          <t>-125.82</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>9112.4</t>
+          <t>10646.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>10143.6</t>
+          <t>11359.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>10903.52</t>
+          <t>10960.76</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1031</t>
+          <t>-713</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-5.682391237693427</t>
+          <t>73.2099091766697</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>171.8879577112803</t>
+          <t>507.1175614556669</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>7084</v>
+        <v>14720</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-36.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>96.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>36.48999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>93.73</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-140.53</t>
+          <t>-132.83</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13322.2</t>
+          <t>9112.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9983.0</t>
+          <t>10143.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10864.78</t>
+          <t>10903.52</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>-1031</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-37.96790922841592</t>
+          <t>-5.682391237693427</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>504.9925253010406</t>
+          <t>171.8879577112803</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>12771</v>
+        <v>7084</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3462,12 +3462,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>346.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-38.52</t>
+          <t>-38.69</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.92</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.87</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-148.06</t>
+          <t>-140.53</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>12815.0</t>
+          <t>13322.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>9174.3</t>
+          <t>9983.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10767.54</t>
+          <t>10864.78</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-136.6879882337716</t>
+          <t>-37.96790922841592</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>353.4993173828061</t>
+          <t>504.9925253010406</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>10867</v>
+        <v>12771</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-35.96</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-40.10</t>
+          <t>-38.52</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,17 +4066,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.94</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-155.16</t>
+          <t>-148.06</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7790.0</t>
+          <t>10867.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>11225.6</t>
+          <t>12815.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>8644.1</t>
+          <t>9174.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>10700.16</t>
+          <t>10767.54</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-225.8129528913312</t>
+          <t>-136.6879882337716</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>328.455473307371</t>
+          <t>353.4993173828061</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>7790</v>
+        <v>10867</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-35.96</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>29.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-40.77</t>
+          <t>-40.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>92.91</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>34.76000000000001</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>37.14</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-161.01</t>
+          <t>-155.16</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7050.0</t>
+          <t>7790.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12072.6</t>
+          <t>11225.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8733.0</t>
+          <t>8644.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>10666.92</t>
+          <t>10700.16</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-326.5890303820044</t>
+          <t>-225.8129528913312</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>610.6265720100564</t>
+          <t>328.455473307371</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>7050</v>
+        <v>7790</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-38.30</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>782.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-40.02</t>
+          <t>-40.77</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,37 +4938,37 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-7.3</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4978,37 +4978,37 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.76000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.14</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-166.10</t>
+          <t>-161.01</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>28133.0</t>
+          <t>7050.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>11174.8</t>
+          <t>12072.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8692.0</t>
+          <t>8733.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>10726.62</t>
+          <t>10666.92</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-496.9918671805608</t>
+          <t>-326.5890303820044</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1071.205764013534</t>
+          <t>610.6265720100564</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>28133</v>
+        <v>7050</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-37.52</t>
+          <t>-38.30</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>782.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-43.93</t>
+          <t>-40.02</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>4.74</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>54.76</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.59</t>
+          <t>-7.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>34.18</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>34.51</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.83</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>12.55</t>
+          <t>26.02</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-170.40</t>
+          <t>-166.10</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30680.70474137931</t>
+          <t>30649.98852223816</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10235.0</t>
+          <t>28133.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>6643.8</t>
+          <t>11174.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6655.2</t>
+          <t>8692.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>10442.72</t>
+          <t>10726.62</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-782.1187092158507</t>
+          <t>-496.9918671805608</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-567.9741675534106</t>
+          <t>1071.205764013534</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>10235</v>
+        <v>28133</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-41.59</t>
+          <t>-37.52</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>48.88</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>36.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>653.213</t>
+          <t>271.149</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-58.91</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-49.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>13729831.0</t>
+          <t>10682520.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>33416468.7</t>
+          <t>33411908.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>30387285.76</t>
+          <t>29853194.9</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-19686637</t>
+          <t>-22729388</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>131142.8910073697</t>
+          <t>-386885.4284653235</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-2168665.852767922</t>
+          <t>-3236041.185565136</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>11367124</v>
+        <v>4725341</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>561.188</t>
+          <t>653.213</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-42.19</t>
+          <t>-58.91</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>18.38</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-34.45</t>
+          <t>-49.91</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-104.97</t>
+          <t>-105.68</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>18901262.2</t>
+          <t>13729831.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>32696459.8</t>
+          <t>33416468.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>30485616.64</t>
+          <t>30387285.76</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-13795197</t>
+          <t>-19686637</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>549289.9353301501</t>
+          <t>131142.8910073697</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-1278011.204030193</t>
+          <t>-2168665.852767922</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>10095558</v>
+        <v>11367124</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6444,17 +6444,17 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>507.54</t>
+          <t>561.188</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>-42.19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-34.45</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.97</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>36519367.2</t>
+          <t>18901262.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>32540510.3</t>
+          <t>32696459.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>30733036.4</t>
+          <t>30485616.64</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3978856</t>
+          <t>-13795197</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>881526.5061229398</t>
+          <t>549289.9353301501</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>176235.0514533557</t>
+          <t>-1278011.204030193</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>8866301</v>
+        <v>10095558</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1035.185</t>
+          <t>507.54</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7133,62 +7133,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-38.61</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-104.10</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>55940470.0</t>
+          <t>36519367.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32435951.2</t>
+          <t>32540510.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>31266005.0</t>
+          <t>30733036.4</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>23504518</t>
+          <t>3978856</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>1009761.316062864</t>
+          <t>881526.5061229398</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2379141.700306527</t>
+          <t>176235.0514533557</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>18358277</v>
+        <v>8866301</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1070.149</t>
+          <t>1035.185</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,72 +7554,72 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.10</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>56141296.2</t>
+          <t>55940470.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>31853386.5</t>
+          <t>32435951.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>31581240.88</t>
+          <t>31266005.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>24287909</t>
+          <t>23504518</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>760783.064382198</t>
+          <t>1009761.316062864</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>4424184.423657246</t>
+          <t>2379141.700306527</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>19961895</v>
+        <v>18358277</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1899.74</t>
+          <t>1070.149</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-11.37</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.31</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,77 +7990,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
           <t>59.09</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>86.36</t>
-        </is>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-104.55</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>53103106.4</t>
+          <t>56141296.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>30684373.7</t>
+          <t>31853386.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>31832273.68</t>
+          <t>31581240.88</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>22418732</t>
+          <t>24287909</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>94710.08996855281</t>
+          <t>760783.064382198</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>7015851.227599084</t>
+          <t>4424184.423657246</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>37224280</v>
+        <v>19961895</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4856.308</t>
+          <t>1899.74</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-16.62</t>
+          <t>-10.72</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>73.06</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>80.63</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-105.46</t>
+          <t>-104.55</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>46491657.4</t>
+          <t>53103106.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>28068835.8</t>
+          <t>30684373.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>31715644.28</t>
+          <t>31832273.68</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>18422821</t>
+          <t>22418732</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-1163679.207782453</t>
+          <t>94710.08996855281</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>8618125.01081603</t>
+          <t>7015851.227599084</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>98186083</v>
+        <v>37224280</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5394.844</t>
+          <t>4856.308</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-15.16</t>
+          <t>-15.94</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>65.63</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,37 +8877,37 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -8917,22 +8917,22 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.42</t>
+          <t>-105.46</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>105971815.0</t>
+          <t>98186083.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>28561653.4</t>
+          <t>46491657.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>20582217.5</t>
+          <t>28068835.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>30693683.24</t>
+          <t>31715644.28</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7979435</t>
+          <t>18422821</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-2942189.06570945</t>
+          <t>-1163679.207782453</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>4067675.629311096</t>
+          <t>8618125.01081603</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>105971815</v>
+        <v>98186083</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1052.024</t>
+          <t>5394.844</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-14.49</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-22.06</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.82</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.42</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>19362408.0</t>
+          <t>105971815.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>8931432.4</t>
+          <t>28561653.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>11459635.1</t>
+          <t>20582217.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>29700594.34</t>
+          <t>30693683.24</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2528202</t>
+          <t>7979435</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-4216709.919349549</t>
+          <t>-2942189.06570945</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3412426.0453142</t>
+          <t>4067675.629311096</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>19362408</v>
+        <v>105971815</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9496,17 +9496,17 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>269.064</t>
+          <t>1052.024</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-7.25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-30.08</t>
+          <t>-22.06</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-45.72</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.43</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4770946.0</t>
+          <t>19362408.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>7565476.8</t>
+          <t>8931432.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>10819850.9</t>
+          <t>11459635.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>32149291.2</t>
+          <t>29700594.34</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-3254374</t>
+          <t>-2528202</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4362943.35099234</t>
+          <t>-4216709.919349549</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-4696833.900303403</t>
+          <t>-3412426.0453142</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>4770946</v>
+        <v>19362408</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>17.55</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>232.654</t>
+          <t>269.064</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.19</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-28.91</t>
+          <t>-30.08</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.38</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>19.25</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-54.39</t>
+          <t>-45.72</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-105.69</t>
+          <t>-106.43</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>69069229.84698276</t>
+          <t>68980304.13916786</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4167035.0</t>
+          <t>4770946.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>8265641.0</t>
+          <t>7565476.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>11626271.8</t>
+          <t>10819850.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>36405486.04</t>
+          <t>32149291.2</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3360630</t>
+          <t>-3254374</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-4302235.978390328</t>
+          <t>-4362943.35099234</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-4800587.268134283</t>
+          <t>-4696833.900303403</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>4167035</v>
+        <v>4770946</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>100.88</t>
+          <t>101.47</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>136.95</t>
+          <t>138.43</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>2865</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-37.94</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.22000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>35.64</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>2018.96</t>
+          <t>518.15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-96.46</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>10871.8</t>
+          <t>8553.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9992.1</t>
+          <t>9599.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>10687.76</t>
+          <t>10349.7</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>-1046</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>170.7364848616841</t>
+          <t>67.99542342574854</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>37.6657122574743</t>
+          <t>-497.0804144718968</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>6181</v>
+        <v>3127</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-35.36</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>77.87</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.64</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>365.87</t>
+          <t>2018.96</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>11052.4</t>
+          <t>10871.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>10895.12</t>
+          <t>10687.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>11445</v>
+        <v>6181</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-36.22</t>
+          <t>-35.36</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>95.52</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>36.59</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>229.08</t>
+          <t>365.87</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>11317.6</t>
+          <t>11052.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>11140.44</t>
+          <t>10895.12</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>15697</v>
+        <v>11445</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-34.66</t>
+          <t>-36.22</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.59</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>142.57</t>
+          <t>229.08</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-119.03</t>
+          <t>-112.10</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>10351.6</t>
+          <t>11317.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>10788.6</t>
+          <t>12066.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>10931.74</t>
+          <t>11140.44</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-437</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>77.1468993095428</t>
+          <t>144.367881711707</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>98.80034504034484</t>
+          <t>514.0832849236103</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>6316</v>
+        <v>15697</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-34.66</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-39.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,72 +2763,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.52</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>142.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-125.82</t>
+          <t>-119.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>10646.4</t>
+          <t>10351.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>11359.5</t>
+          <t>10788.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>10960.76</t>
+          <t>10931.74</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-713</t>
+          <t>-437</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>73.2099091766697</t>
+          <t>77.1468993095428</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>507.1175614556669</t>
+          <t>98.80034504034484</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>14720</v>
+        <v>6316</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-39.10</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>36.48999999999999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>36.71</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>108.68</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-132.83</t>
+          <t>-125.82</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>9112.4</t>
+          <t>10646.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10143.6</t>
+          <t>11359.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10903.52</t>
+          <t>10960.76</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1031</t>
+          <t>-713</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-5.682391237693427</t>
+          <t>73.2099091766697</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>171.8879577112803</t>
+          <t>507.1175614556669</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>7084</v>
+        <v>14720</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-36.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>96.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>36.48999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>93.73</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-140.53</t>
+          <t>-132.83</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>13322.2</t>
+          <t>9112.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>9983.0</t>
+          <t>10143.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10864.78</t>
+          <t>10903.52</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>-1031</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-37.96790922841592</t>
+          <t>-5.682391237693427</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>504.9925253010406</t>
+          <t>171.8879577112803</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>12771</v>
+        <v>7084</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>346.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-38.52</t>
+          <t>-38.69</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.92</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.87</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-148.06</t>
+          <t>-140.53</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>12815.0</t>
+          <t>13322.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>9174.3</t>
+          <t>9983.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>10767.54</t>
+          <t>10864.78</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-136.6879882337716</t>
+          <t>-37.96790922841592</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>353.4993173828061</t>
+          <t>504.9925253010406</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>10867</v>
+        <v>12771</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-35.96</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-40.10</t>
+          <t>-38.52</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4522,57 +4522,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.94</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-155.16</t>
+          <t>-148.06</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7790.0</t>
+          <t>10867.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>11225.6</t>
+          <t>12815.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>8644.1</t>
+          <t>9174.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>10700.16</t>
+          <t>10767.54</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-225.8129528913312</t>
+          <t>-136.6879882337716</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>328.455473307371</t>
+          <t>353.4993173828061</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>7790</v>
+        <v>10867</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-35.96</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4700,17 +4700,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>29.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-40.77</t>
+          <t>-40.10</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,72 +4943,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>92.91</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>34.76000000000001</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>37.14</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-161.01</t>
+          <t>-155.16</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7050.0</t>
+          <t>7790.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>12072.6</t>
+          <t>11225.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8733.0</t>
+          <t>8644.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>10666.92</t>
+          <t>10700.16</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-326.5890303820044</t>
+          <t>-225.8129528913312</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>610.6265720100564</t>
+          <t>328.455473307371</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>7050</v>
+        <v>7790</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-38.30</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>782.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-40.02</t>
+          <t>-40.77</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,32 +5379,32 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.85</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>60.28</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-7.3</t>
+          <t>-6.95</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -5414,37 +5414,37 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>34.76000000000001</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.14</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.83</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>26.02</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-166.10</t>
+          <t>-161.01</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30649.98852223816</t>
+          <t>30612.79727793696</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>28133.0</t>
+          <t>7050.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>11174.8</t>
+          <t>12072.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>8692.0</t>
+          <t>8733.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>10726.62</t>
+          <t>10666.92</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-496.9918671805608</t>
+          <t>-326.5890303820044</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1071.205764013534</t>
+          <t>610.6265720100564</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>28133</v>
+        <v>7050</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-37.52</t>
+          <t>-38.30</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.88</t>
+          <t>48.64</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>35.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>36.05</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>271.149</t>
+          <t>356.458</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-74.28</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-49.07</t>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.47</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>10682520.2</t>
+          <t>8255008.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>33411908.2</t>
+          <t>32097739.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>29853194.9</t>
+          <t>29138835.12</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-22729388</t>
+          <t>-23842731</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-386885.4284653235</t>
+          <t>-910464.5569912827</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3236041.185565136</t>
+          <t>-3790149.763884058</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>4725341</v>
+        <v>6220716</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>653.213</t>
+          <t>271.149</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-58.91</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-49.07</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>13729831.0</t>
+          <t>10682520.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>33416468.7</t>
+          <t>33411908.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>30387285.76</t>
+          <t>29853194.9</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-19686637</t>
+          <t>-22729388</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>131142.8910073697</t>
+          <t>-386885.4284653235</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-2168665.852767922</t>
+          <t>-3236041.185565136</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>11367124</v>
+        <v>4725341</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>561.188</t>
+          <t>653.213</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-42.19</t>
+          <t>-58.91</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>18.38</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-34.45</t>
+          <t>-49.91</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-104.97</t>
+          <t>-105.68</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>18901262.2</t>
+          <t>13729831.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>32696459.8</t>
+          <t>33416468.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>30485616.64</t>
+          <t>30387285.76</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-13795197</t>
+          <t>-19686637</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>549289.9353301501</t>
+          <t>131142.8910073697</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1278011.204030193</t>
+          <t>-2168665.852767922</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>10095558</v>
+        <v>11367124</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6880,17 +6880,17 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>507.54</t>
+          <t>561.188</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>-42.19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-34.45</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.97</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>36519367.2</t>
+          <t>18901262.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32540510.3</t>
+          <t>32696459.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>30733036.4</t>
+          <t>30485616.64</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>3978856</t>
+          <t>-13795197</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>881526.5061229398</t>
+          <t>549289.9353301501</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>176235.0514533557</t>
+          <t>-1278011.204030193</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>8866301</v>
+        <v>10095558</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1035.185</t>
+          <t>507.54</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7569,62 +7569,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-38.61</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-104.10</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>55940470.0</t>
+          <t>36519367.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32435951.2</t>
+          <t>32540510.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>31266005.0</t>
+          <t>30733036.4</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>23504518</t>
+          <t>3978856</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>1009761.316062864</t>
+          <t>881526.5061229398</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>2379141.700306527</t>
+          <t>176235.0514533557</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>18358277</v>
+        <v>8866301</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1070.149</t>
+          <t>1035.185</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,72 +7990,72 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.10</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>56141296.2</t>
+          <t>55940470.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>31853386.5</t>
+          <t>32435951.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>31581240.88</t>
+          <t>31266005.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>24287909</t>
+          <t>23504518</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>760783.064382198</t>
+          <t>1009761.316062864</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>4424184.423657246</t>
+          <t>2379141.700306527</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>19961895</v>
+        <v>18358277</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1899.74</t>
+          <t>1070.149</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-10.72</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
           <t>59.09</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>86.36</t>
-        </is>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.55</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>53103106.4</t>
+          <t>56141296.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>30684373.7</t>
+          <t>31853386.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>31832273.68</t>
+          <t>31581240.88</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>22418732</t>
+          <t>24287909</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>94710.08996855281</t>
+          <t>760783.064382198</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>7015851.227599084</t>
+          <t>4424184.423657246</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>37224280</v>
+        <v>19961895</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4856.308</t>
+          <t>1899.74</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-15.94</t>
+          <t>-10.09</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>73.06</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>80.63</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-105.46</t>
+          <t>-104.55</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>46491657.4</t>
+          <t>53103106.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>28068835.8</t>
+          <t>30684373.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>31715644.28</t>
+          <t>31832273.68</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>18422821</t>
+          <t>22418732</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-1163679.207782453</t>
+          <t>94710.08996855281</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>8618125.01081603</t>
+          <t>7015851.227599084</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>98186083</v>
+        <v>37224280</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5394.844</t>
+          <t>4856.308</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-14.49</t>
+          <t>-15.27</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>65.63</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,12 +9298,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,37 +9313,37 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -9353,22 +9353,22 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-106.42</t>
+          <t>-105.46</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>105971815.0</t>
+          <t>98186083.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>28561653.4</t>
+          <t>46491657.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>20582217.5</t>
+          <t>28068835.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>30693683.24</t>
+          <t>31715644.28</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7979435</t>
+          <t>18422821</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-2942189.06570945</t>
+          <t>-1163679.207782453</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>4067675.629311096</t>
+          <t>8618125.01081603</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>105971815</v>
+        <v>98186083</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1052.024</t>
+          <t>5394.844</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-7.25</t>
+          <t>-13.83</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-22.06</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.42</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>19362408.0</t>
+          <t>105971815.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>8931432.4</t>
+          <t>28561653.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>11459635.1</t>
+          <t>20582217.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>29700594.34</t>
+          <t>30693683.24</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2528202</t>
+          <t>7979435</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4216709.919349549</t>
+          <t>-2942189.06570945</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-3412426.0453142</t>
+          <t>4067675.629311096</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>19362408</v>
+        <v>105971815</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>269.064</t>
+          <t>1052.024</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.19</t>
+          <t>-6.63</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-30.08</t>
+          <t>-22.06</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>356</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>25.93</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>19.25</t>
+          <t>19.21</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-45.72</t>
+          <t>-22.12</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.43</t>
+          <t>-106.80</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>68980304.13916786</t>
+          <t>68894846.78939828</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4770946.0</t>
+          <t>19362408.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>7565476.8</t>
+          <t>8931432.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>10819850.9</t>
+          <t>11459635.1</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>32149291.2</t>
+          <t>29700594.34</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3254374</t>
+          <t>-2528202</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-4362943.35099234</t>
+          <t>-4216709.919349549</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-4696833.900303403</t>
+          <t>-3412426.0453142</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>4770946</v>
+        <v>19362408</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>101.47</t>
+          <t>102.06</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>138.43</t>
+          <t>141.44</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
+          <t>18.85</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>17.55</t>
-        </is>
-      </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-38.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,72 +1019,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.22000000000001</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>36.45</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>518.15</t>
+          <t>207.15</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-96.46</t>
+          <t>-92.66</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>8553.2</t>
+          <t>7725.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9599.8</t>
+          <t>9038.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>10349.7</t>
+          <t>10088.66</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1312</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>67.99542342574854</t>
+          <t>-85.55397907369867</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-497.0804144718968</t>
+          <t>-930.0756928206583</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>3127</v>
+        <v>2179</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-37.94</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1455,72 +1455,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.22000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>35.64</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>36.49</t>
+          <t>36.45</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>2018.96</t>
+          <t>518.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-96.46</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>10871.8</t>
+          <t>8553.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9992.1</t>
+          <t>9599.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>10687.76</t>
+          <t>10349.7</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>-1046</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>170.7364848616841</t>
+          <t>67.99542342574854</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>37.6657122574743</t>
+          <t>-497.0804144718968</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>6181</v>
+        <v>3127</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-35.36</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,72 +1891,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>77.87</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>35.64</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>36.49</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>365.87</t>
+          <t>2018.96</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>11052.4</t>
+          <t>10871.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>10895.12</t>
+          <t>10687.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>11445</v>
+        <v>6181</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-36.22</t>
+          <t>-35.36</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2327,72 +2327,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>95.52</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>35.39</t>
+          <t>35.51</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>36.59</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>229.08</t>
+          <t>365.87</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>11317.6</t>
+          <t>11052.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>11140.44</t>
+          <t>10895.12</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>15697</v>
+        <v>11445</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-34.66</t>
+          <t>-36.22</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.59</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>142.57</t>
+          <t>229.08</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.03</t>
+          <t>-112.10</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>10351.6</t>
+          <t>11317.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>10788.6</t>
+          <t>12066.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>10931.74</t>
+          <t>11140.44</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-437</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>77.1468993095428</t>
+          <t>144.367881711707</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>98.80034504034484</t>
+          <t>514.0832849236103</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>6316</v>
+        <v>15697</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-34.66</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-39.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3199,72 +3199,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.52</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>142.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-125.82</t>
+          <t>-119.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>10646.4</t>
+          <t>10351.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>11359.5</t>
+          <t>10788.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>10960.76</t>
+          <t>10931.74</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-713</t>
+          <t>-437</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>73.2099091766697</t>
+          <t>77.1468993095428</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>507.1175614556669</t>
+          <t>98.80034504034484</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>14720</v>
+        <v>6316</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-39.10</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3635,72 +3635,72 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>36.48999999999999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>36.79</t>
+          <t>36.71</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>108.68</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-132.83</t>
+          <t>-125.82</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>9112.4</t>
+          <t>10646.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>10143.6</t>
+          <t>11359.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>10903.52</t>
+          <t>10960.76</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1031</t>
+          <t>-713</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-5.682391237693427</t>
+          <t>73.2099091766697</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>171.8879577112803</t>
+          <t>507.1175614556669</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>7084</v>
+        <v>14720</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-36.57</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4071,72 +4071,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>96.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>36.48999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>34.87</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>36.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>93.73</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-140.53</t>
+          <t>-132.83</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>13322.2</t>
+          <t>9112.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>9983.0</t>
+          <t>10143.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>10864.78</t>
+          <t>10903.52</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>-1031</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-37.96790922841592</t>
+          <t>-5.682391237693427</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>504.9925253010406</t>
+          <t>171.8879577112803</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>12771</v>
+        <v>7084</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>346.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-38.52</t>
+          <t>-38.69</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4507,72 +4507,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.92</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>34.87</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>36.94</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-148.06</t>
+          <t>-140.53</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>12815.0</t>
+          <t>13322.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>9174.3</t>
+          <t>9983.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>10767.54</t>
+          <t>10864.78</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-136.6879882337716</t>
+          <t>-37.96790922841592</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>353.4993173828061</t>
+          <t>504.9925253010406</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>10867</v>
+        <v>12771</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-35.96</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-40.10</t>
+          <t>-38.52</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>34.64</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>36.94</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-155.16</t>
+          <t>-148.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7790.0</t>
+          <t>10867.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>11225.6</t>
+          <t>12815.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>8644.1</t>
+          <t>9174.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>10700.16</t>
+          <t>10767.54</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-225.8129528913312</t>
+          <t>-136.6879882337716</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>328.455473307371</t>
+          <t>353.4993173828061</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>7790</v>
+        <v>10867</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-35.96</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>29.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-40.77</t>
+          <t>-40.10</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5379,72 +5379,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>60.28</t>
+          <t>92.91</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>-6.49</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>34.76000000000001</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>34.64</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>37.14</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-161.01</t>
+          <t>-155.16</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30612.79727793696</t>
+          <t>30573.67811158799</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7050.0</t>
+          <t>7790.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>12072.6</t>
+          <t>11225.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>8733.0</t>
+          <t>8644.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>10666.92</t>
+          <t>10700.16</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-326.5890303820044</t>
+          <t>-225.8129528913312</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>610.6265720100564</t>
+          <t>328.455473307371</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>7050</v>
+        <v>7790</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-38.30</t>
+          <t>-37.61</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.43</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.27</t>
+          <t>11.24</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>48.64</t>
+          <t>49.21</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>35.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,42 +5679,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>811.45</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>0.57</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>356.458</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>17.35</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.59</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-74.28</t>
+          <t>-59.12</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-3.47</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
           <t>-0.40</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-3.65</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t>-23.36</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-107.22</t>
+          <t>-107.67</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>8255008.0</t>
+          <t>9383601.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>32097739.0</t>
+          <t>22951484.1</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>29138835.12</t>
+          <t>28459246.14</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-23842731</t>
+          <t>-13567883</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-910464.5569912827</t>
+          <t>-1302951.667394193</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3790149.763884058</t>
+          <t>-3461630.774610199</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>6220716</v>
+        <v>14509266</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>271.149</t>
+          <t>356.458</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-74.28</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>18.94</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-49.07</t>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-106.47</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>10682520.2</t>
+          <t>8255008.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>33411908.2</t>
+          <t>32097739.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>29853194.9</t>
+          <t>29138835.12</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-22729388</t>
+          <t>-23842731</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-386885.4284653235</t>
+          <t>-910464.5569912827</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3236041.185565136</t>
+          <t>-3790149.763884058</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>4725341</v>
+        <v>6220716</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>653.213</t>
+          <t>271.149</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-58.91</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>18.38</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>18.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-49.07</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>13729831.0</t>
+          <t>10682520.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33416468.7</t>
+          <t>33411908.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>30387285.76</t>
+          <t>29853194.9</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-19686637</t>
+          <t>-22729388</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>131142.8910073697</t>
+          <t>-386885.4284653235</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-2168665.852767922</t>
+          <t>-3236041.185565136</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>11367124</v>
+        <v>4725341</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>561.188</t>
+          <t>653.213</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-42.19</t>
+          <t>-58.91</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,17 +7118,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>18.48</t>
+          <t>18.38</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-34.45</t>
+          <t>-49.91</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-104.97</t>
+          <t>-105.68</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>18901262.2</t>
+          <t>13729831.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32696459.8</t>
+          <t>33416468.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>30485616.64</t>
+          <t>30387285.76</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-13795197</t>
+          <t>-19686637</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>549289.9353301501</t>
+          <t>131142.8910073697</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1278011.204030193</t>
+          <t>-2168665.852767922</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>10095558</v>
+        <v>11367124</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7316,17 +7316,17 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>507.54</t>
+          <t>561.188</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>-42.19</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>18.48</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>19.06</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-34.45</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.97</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>36519367.2</t>
+          <t>18901262.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32540510.3</t>
+          <t>32696459.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>30733036.4</t>
+          <t>30485616.64</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>3978856</t>
+          <t>-13795197</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>881526.5061229398</t>
+          <t>549289.9353301501</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>176235.0514533557</t>
+          <t>-1278011.204030193</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>8866301</v>
+        <v>10095558</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1035.185</t>
+          <t>507.54</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.55</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>19.06</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-38.61</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-104.10</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>55940470.0</t>
+          <t>36519367.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>32435951.2</t>
+          <t>32540510.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>31266005.0</t>
+          <t>30733036.4</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>23504518</t>
+          <t>3978856</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>1009761.316062864</t>
+          <t>881526.5061229398</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2379141.700306527</t>
+          <t>176235.0514533557</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>18358277</v>
+        <v>8866301</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1070.149</t>
+          <t>1035.185</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.9</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,72 +8426,72 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.10</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>56141296.2</t>
+          <t>55940470.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>31853386.5</t>
+          <t>32435951.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>31581240.88</t>
+          <t>31266005.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>24287909</t>
+          <t>23504518</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>760783.064382198</t>
+          <t>1009761.316062864</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>4424184.423657246</t>
+          <t>2379141.700306527</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>19961895</v>
+        <v>18358277</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1899.74</t>
+          <t>1070.149</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-10.09</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
           <t>59.09</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>86.36</t>
-        </is>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.69</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>19.18</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.55</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>53103106.4</t>
+          <t>56141296.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>30684373.7</t>
+          <t>31853386.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>31832273.68</t>
+          <t>31581240.88</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>22418732</t>
+          <t>24287909</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>94710.08996855281</t>
+          <t>760783.064382198</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>7015851.227599084</t>
+          <t>4424184.423657246</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>37224280</v>
+        <v>19961895</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4856.308</t>
+          <t>1899.74</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-6.7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>73.06</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>18.73</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>19.2</t>
+          <t>19.18</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>80.63</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-105.46</t>
+          <t>-104.55</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>46491657.4</t>
+          <t>53103106.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>28068835.8</t>
+          <t>30684373.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>31715644.28</t>
+          <t>31832273.68</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>18422821</t>
+          <t>22418732</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-1163679.207782453</t>
+          <t>94710.08996855281</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>8618125.01081603</t>
+          <t>7015851.227599084</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>98186083</v>
+        <v>37224280</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5394.844</t>
+          <t>4856.308</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-13.83</t>
+          <t>-11.73</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>65.63</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,37 +9749,37 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.73</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -9789,22 +9789,22 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-106.42</t>
+          <t>-105.46</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>105971815.0</t>
+          <t>98186083.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>28561653.4</t>
+          <t>46491657.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>20582217.5</t>
+          <t>28068835.8</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>30693683.24</t>
+          <t>31715644.28</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7979435</t>
+          <t>18422821</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-2942189.06570945</t>
+          <t>-1163679.207782453</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4067675.629311096</t>
+          <t>8618125.01081603</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>105971815</v>
+        <v>98186083</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1052.024</t>
+          <t>5394.844</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.63</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-22.06</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>38.09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>811</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>7.34</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>18.02</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>19.2</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.68</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-22.12</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.80</t>
+          <t>-106.42</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>68894846.78939828</t>
+          <t>68827420.54077253</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>19362408.0</t>
+          <t>105971815.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>8931432.4</t>
+          <t>28561653.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>11459635.1</t>
+          <t>20582217.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>29700594.34</t>
+          <t>30693683.24</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2528202</t>
+          <t>7979435</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-4216709.919349549</t>
+          <t>-2942189.06570945</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-3412426.0453142</t>
+          <t>4067675.629311096</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>19362408</v>
+        <v>105971815</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>14.55</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>102.06</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>141.44</t>
+          <t>152.95</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>37.22</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>35.9</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>36.42</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>36.42</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>2179.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>7725.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>7725.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>9038.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>10088.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>10088.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-930.0756928206583</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>2179</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2179.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>37.22000000000001</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>35.77</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>36.45</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>36.45</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>3127.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>8553.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>8553.200000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>9599.8</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>10349.7</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>10349.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-497.0804144718968</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>3127</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3127.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>37.1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>35.64</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>36.49</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>35.64</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>36.49</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6181.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>10871.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>10871.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>9992.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>10687.76</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>10687.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>37.6657122574743</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6181</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6181.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>37.05</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>35.51</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>36.53</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>35.51</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>36.53</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>11445.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>11052.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>11052.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>12187.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>10895.12</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>10895.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>473.0292607188057</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>11445</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>11445.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>37.06</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>35.39</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>36.59</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>35.39</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>36.59</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>15697.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>11317.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>11317.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>12066.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>11140.44</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>11140.44</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>514.0832849236103</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>15697</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>15697.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>36.91</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>36.64</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>36.64</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>6316.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>10351.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>10351.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>10788.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>10931.74</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>10931.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>98.80034504034484</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>6316</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>6316.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>36.69</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>35.12</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>36.71</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36.71</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>14720.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>10646.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>10646.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>11359.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>10960.76</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>10960.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>507.1175614556669</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>14720</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>14720.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>36.48999999999999</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>35.01</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>36.79</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>35.01</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36.79</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>7084.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>9112.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>9112.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>10143.6</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>10903.52</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>10903.52</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>171.8879577112803</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>7084</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>7084.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>36.29</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>34.87</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36.86</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>12771.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>13322.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>13322.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>9983.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>10864.78</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>10864.78</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>504.9925253010406</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>12771</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>12771.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>35.66</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>34.76</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>36.94</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36.94</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>10867.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>12815.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>12815</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>9174.3</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>10767.54</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>10767.54</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>353.4993173828061</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>10867</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>10867.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>35.16</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>34.64</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>37.03</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>34.64</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>37.03</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>7790.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>11225.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>11225.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>8644.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>10700.16</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>10700.16</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>328.455473307371</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>7790</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>7790.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>17.52</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>18.15</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>18.86</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>14509266.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>9383601.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>9383601</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>22951484.1</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>28459246.14</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>28459246.14</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-3461630.774610199</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>14509266</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>14509266.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>17.42</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>18.2</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>18.89</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>18.89</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>6220716.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>8255008.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>8255008</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>32097739.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>29138835.12</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>29138835.12</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-3790149.763884058</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>6220716</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>6220716.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>17.46</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>18.28</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>18.94</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>18.94</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>4725341.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>10682520.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>10682520.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>33411908.2</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>29853194.9</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>29853194.9</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-3236041.185565136</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>4725341</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>4725341.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>17.65</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>18.38</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>18.99</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>18.99</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>11367124.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>13729831.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>13729831</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>33416468.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>30387285.76</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>30387285.76</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-2168665.852767922</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>11367124</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>11367124.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>18.04</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>18.48</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>19.03</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>10095558.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>18901262.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>18901262.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>32696459.8</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>30485616.64</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>30485616.64</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1278011.204030193</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>10095558</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>10095558.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>18.45</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>18.55</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>19.06</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>19.06</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>8866301.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>36519367.2</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>36519367.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>32540510.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>30733036.4</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>30733036.4</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>176235.0514533557</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>8866301</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>8866301.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>18.92</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>18.63</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>19.1</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>18358277.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>55940470.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>55940470</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>32435951.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>31266005.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>31266005</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>2379141.700306527</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>18358277</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>18358277.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>19.11</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>18.69</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>19.16</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>19.16</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>19961895.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>56141296.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>56141296.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>31853386.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>31581240.88</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>31581240.88</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>4424184.423657246</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>19961895</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>19961895.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>19.03</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>18.74</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>19.18</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>19.18</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>37224280.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>53103106.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>53103106.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>30684373.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>31832273.68</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>31832273.68</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>7015851.227599084</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>37224280</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>37224280.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>18.77</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>18.73</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>19.2</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>98186083.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>46491657.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>46491657.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>28068835.8</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>31715644.28</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>31715644.28</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>8618125.01081603</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>98186083</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>98186083.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,21 +10087,17 @@
           <t>18.4</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AM23" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AO23" t="inlineStr">
         <is>
           <t>18.68</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>18.68</t>
-        </is>
-      </c>
       <c r="AP23" t="inlineStr">
         <is>
           <t>23.98</t>
@@ -10268,20 +10138,16 @@
           <t>105971815.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>28561653.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>28561653.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>20582217.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>30693683.24</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>30693683.24</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>4067675.629311096</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>105971815</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>105971815.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-38.60</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>35.9</v>
+        <v>36.03</v>
       </c>
       <c r="AN2" t="n">
-        <v>36.42</v>
+        <v>36.4</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>207.15</t>
+          <t>113.09</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.66</t>
+          <t>-89.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>7725.8</v>
+        <v>5058.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>9038.7</t>
+          <t>8187.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>10088.66</v>
+        <v>9806.860000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1312</t>
+          <t>-3129</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-85.55397907369867</t>
+          <t>-256.4565200384027</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-930.0756928206583</t>
+          <t>-1196.420495344275</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-36.05</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,102 +1338,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-0.54</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-14.53</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-99.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-02-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-03-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2024-06-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2024-06-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>60.4</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>60.1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>73.9</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>67.5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-38.27</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-10.52</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-0.27</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-10.90</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-99.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-02-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-03-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2024-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024-06-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>60.4</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>60.1</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>73.9</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>67.5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-38.10</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-10.52</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-0.80</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.22000000000001</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>35.77</v>
+        <v>35.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>36.45</v>
+        <v>36.42</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>518.15</t>
+          <t>207.15</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-96.46</t>
+          <t>-92.66</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>8553.200000000001</v>
+        <v>7725.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9599.8</t>
+          <t>9038.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10349.7</v>
+        <v>10088.66</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1312</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>67.99542342574854</t>
+          <t>-85.55397907369867</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-497.0804144718968</t>
+          <t>-930.0756928206583</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-37.94</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.22000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>35.64</v>
+        <v>35.77</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.49</v>
+        <v>36.45</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2018.96</t>
+          <t>518.15</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-96.46</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>10871.8</v>
+        <v>8553.200000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>9992.1</t>
+          <t>9599.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10687.76</v>
+        <v>10349.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>-1046</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>170.7364848616841</t>
+          <t>67.99542342574854</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>37.6657122574743</t>
+          <t>-497.0804144718968</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-35.36</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>77.87</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>35.51</v>
+        <v>35.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>36.53</v>
+        <v>36.49</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>365.87</t>
+          <t>2018.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>11052.4</v>
+        <v>10871.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10895.12</v>
+        <v>10687.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-36.22</t>
+          <t>-35.36</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>95.52</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>35.39</v>
+        <v>35.51</v>
       </c>
       <c r="AN6" t="n">
-        <v>36.59</v>
+        <v>36.53</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>229.08</t>
+          <t>365.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>11317.6</v>
+        <v>11052.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>11140.44</v>
+        <v>10895.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-34.66</t>
+          <t>-36.22</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>35.26</v>
+        <v>35.39</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.64</v>
+        <v>36.59</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>142.57</t>
+          <t>229.08</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-119.03</t>
+          <t>-112.10</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>10351.6</v>
+        <v>11317.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>10788.6</t>
+          <t>12066.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10931.74</v>
+        <v>11140.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-437</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>77.1468993095428</t>
+          <t>144.367881711707</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>98.80034504034484</t>
+          <t>514.0832849236103</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-34.66</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-39.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.52</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>35.12</v>
+        <v>35.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>36.71</v>
+        <v>36.64</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>142.57</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-125.82</t>
+          <t>-119.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>10646.4</v>
+        <v>10351.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11359.5</t>
+          <t>10788.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10960.76</v>
+        <v>10931.74</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-713</t>
+          <t>-437</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>73.2099091766697</t>
+          <t>77.1468993095428</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>507.1175614556669</t>
+          <t>98.80034504034484</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-39.10</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>36.48999999999999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>35.01</v>
+        <v>35.12</v>
       </c>
       <c r="AN9" t="n">
-        <v>36.79</v>
+        <v>36.71</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>108.68</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-132.83</t>
+          <t>-125.82</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>9112.4</v>
+        <v>10646.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>10143.6</t>
+          <t>11359.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10903.52</v>
+        <v>10960.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1031</t>
+          <t>-713</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-5.682391237693427</t>
+          <t>73.2099091766697</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>171.8879577112803</t>
+          <t>507.1175614556669</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-36.57</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>96.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>36.48999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>34.87</v>
+        <v>35.01</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.86</v>
+        <v>36.79</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>93.73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-140.53</t>
+          <t>-132.83</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>13322.2</v>
+        <v>9112.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>9983.0</t>
+          <t>10143.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10864.78</v>
+        <v>10903.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>-1031</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-37.96790922841592</t>
+          <t>-5.682391237693427</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>504.9925253010406</t>
+          <t>171.8879577112803</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>346.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-38.52</t>
+          <t>-38.69</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.92</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>34.76</v>
+        <v>34.87</v>
       </c>
       <c r="AN11" t="n">
-        <v>36.94</v>
+        <v>36.86</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-148.06</t>
+          <t>-140.53</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>12815</v>
+        <v>13322.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>9174.3</t>
+          <t>9983.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10767.54</v>
+        <v>10864.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-136.6879882337716</t>
+          <t>-37.96790922841592</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>353.4993173828061</t>
+          <t>504.9925253010406</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-35.96</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>299.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>39.68</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-40.10</t>
+          <t>-38.52</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,17 +5314,17 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-5.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.49</t>
+          <t>-6.46</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>34.64</v>
+        <v>34.76</v>
       </c>
       <c r="AN12" t="n">
-        <v>37.03</v>
+        <v>36.94</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>59.14</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-155.16</t>
+          <t>-148.06</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30573.67811158799</t>
+          <t>30535.05642857143</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7790.0</t>
+          <t>10867.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>11225.6</v>
+        <v>12815</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>8644.1</t>
+          <t>9174.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10700.16</v>
+        <v>10767.54</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-225.8129528913312</t>
+          <t>-136.6879882337716</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>328.455473307371</t>
+          <t>353.4993173828061</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>7790.0</t>
+          <t>10867.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-37.61</t>
+          <t>-35.96</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.43</t>
+          <t>9.49</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.24</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.21</t>
+          <t>49.25</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>35.9</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>811.45</t>
+          <t>381.935</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-59.12</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.86</v>
+        <v>18.82</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-23.36</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-107.67</t>
+          <t>-107.83</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>9383601</v>
+        <v>8737475.800000001</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>22951484.1</t>
+          <t>13819369.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>28459246.14</v>
+        <v>28136264.12</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-13567883</t>
+          <t>-5081893</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-1302951.667394193</t>
+          <t>-1674567.0666802</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3461630.774610199</t>
+          <t>-3718451.762753243</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,24 +5996,24 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>18.05</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
       <c r="CH13" t="inlineStr">
         <is>
           <t>17.18</t>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>356.458</t>
+          <t>811.45</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-74.28</t>
+          <t>-59.12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-3.47</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
           <t>-0.40</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>-3.65</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>18.2</v>
+        <v>18.15</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.89</v>
+        <v>18.86</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t>-23.36</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.22</t>
+          <t>-107.67</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>8255008</v>
+        <v>9383601</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>32097739.0</t>
+          <t>22951484.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>29138835.12</v>
+        <v>28459246.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-23842731</t>
+          <t>-13567883</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-910464.5569912827</t>
+          <t>-1302951.667394193</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3790149.763884058</t>
+          <t>-3461630.774610199</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>271.149</t>
+          <t>356.458</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-74.28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>18.28</v>
+        <v>18.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.94</v>
+        <v>18.89</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-49.07</t>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-106.47</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>10682520.2</v>
+        <v>8255008</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>33411908.2</t>
+          <t>32097739.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>29853194.9</v>
+        <v>29138835.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-22729388</t>
+          <t>-23842731</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-386885.4284653235</t>
+          <t>-910464.5569912827</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3236041.185565136</t>
+          <t>-3790149.763884058</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>653.213</t>
+          <t>271.149</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-58.91</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>18.38</v>
+        <v>18.28</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.99</v>
+        <v>18.94</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-49.07</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>13729831</v>
+        <v>10682520.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>33416468.7</t>
+          <t>33411908.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>30387285.76</v>
+        <v>29853194.9</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-19686637</t>
+          <t>-22729388</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>131142.8910073697</t>
+          <t>-386885.4284653235</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-2168665.852767922</t>
+          <t>-3236041.185565136</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>561.188</t>
+          <t>653.213</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-42.19</t>
+          <t>-58.91</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>18.48</v>
+        <v>18.38</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.03</v>
+        <v>18.99</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-34.45</t>
+          <t>-49.91</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-104.97</t>
+          <t>-105.68</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>18901262.2</v>
+        <v>13729831</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32696459.8</t>
+          <t>33416468.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>30485616.64</v>
+        <v>30387285.76</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-13795197</t>
+          <t>-19686637</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>549289.9353301501</t>
+          <t>131142.8910073697</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1278011.204030193</t>
+          <t>-2168665.852767922</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7656,17 +7656,17 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="CJ17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>507.54</t>
+          <t>561.188</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>-42.19</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>18.55</v>
+        <v>18.48</v>
       </c>
       <c r="AN18" t="n">
-        <v>19.06</v>
+        <v>19.03</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-34.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.97</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>36519367.2</v>
+        <v>18901262.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>32540510.3</t>
+          <t>32696459.8</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>30733036.4</v>
+        <v>30485616.64</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>3978856</t>
+          <t>-13795197</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>881526.5061229398</t>
+          <t>549289.9353301501</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>176235.0514533557</t>
+          <t>-1278011.204030193</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="CJ18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1035.185</t>
+          <t>507.54</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8339,58 +8339,58 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>18.63</v>
+        <v>18.55</v>
       </c>
       <c r="AN19" t="n">
-        <v>19.1</v>
+        <v>19.06</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-38.61</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.10</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>55940470</v>
+        <v>36519367.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>32435951.2</t>
+          <t>32540510.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>31266005</v>
+        <v>30733036.4</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>23504518</t>
+          <t>3978856</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>1009761.316062864</t>
+          <t>881526.5061229398</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>2379141.700306527</t>
+          <t>176235.0514533557</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8606,14 +8606,14 @@
       </c>
       <c r="CJ19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1070.149</t>
+          <t>1035.185</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,68 +8754,68 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>18.69</v>
+        <v>18.63</v>
       </c>
       <c r="AN20" t="n">
-        <v>19.16</v>
+        <v>19.1</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.10</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>56141296.2</v>
+        <v>55940470</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>31853386.5</t>
+          <t>32435951.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>31581240.88</v>
+        <v>31266005</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>24287909</t>
+          <t>23504518</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>760783.064382198</t>
+          <t>1009761.316062864</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>4424184.423657246</t>
+          <t>2379141.700306527</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="CJ20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1899.74</t>
+          <t>1070.149</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
           <t>59.09</t>
         </is>
       </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>86.36</t>
-        </is>
-      </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AN21" t="n">
-        <v>19.18</v>
+        <v>19.16</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.55</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>53103106.4</v>
+        <v>56141296.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>30684373.7</t>
+          <t>31853386.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>31832273.68</v>
+        <v>31581240.88</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>22418732</t>
+          <t>24287909</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>94710.08996855281</t>
+          <t>760783.064382198</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>7015851.227599084</t>
+          <t>4424184.423657246</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,22 +9371,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="CJ21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4856.308</t>
+          <t>1899.74</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-11.73</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>73.06</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>18.73</v>
+        <v>18.74</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.2</v>
+        <v>19.18</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>80.63</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-105.46</t>
+          <t>-104.55</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>46491657.4</v>
+        <v>53103106.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>28068835.8</t>
+          <t>30684373.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>31715644.28</v>
+        <v>31832273.68</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>18422821</t>
+          <t>22418732</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-1163679.207782453</t>
+          <t>94710.08996855281</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>8618125.01081603</t>
+          <t>7015851.227599084</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="CJ22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5394.844</t>
+          <t>4856.308</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-10.8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>65.63</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>38.09</t>
+          <t>34.29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>7.34</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>18.77</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>18.68</v>
+        <v>18.73</v>
       </c>
       <c r="AN23" t="n">
         <v>19.2</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>18.74</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>70.05</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-106.42</t>
+          <t>-105.46</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>68827420.54077253</t>
+          <t>68743806.22285715</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>105971815.0</t>
+          <t>98186083.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>28561653.4</v>
+        <v>46491657.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>20582217.5</t>
+          <t>28068835.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>30693683.24</v>
+        <v>31715644.28</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>7979435</t>
+          <t>18422821</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-2942189.06570945</t>
+          <t>-1163679.207782453</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>4067675.629311096</t>
+          <t>8618125.01081603</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>105971815.0</t>
+          <t>98186083.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>23.84</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>106.18</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>152.95</t>
+          <t>148.15</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>19.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-38.22</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-38.60</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>36.03</v>
+        <v>36.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>36.4</v>
+        <v>36.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>113.09</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-89.77</t>
+          <t>-86.91</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>5058.2</v>
+        <v>3849.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>8187.9</t>
+          <t>7451.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9806.860000000001</v>
+        <v>9807.120000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3129</t>
+          <t>-3601</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-256.4565200384027</t>
+          <t>-390.0249546059099</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1196.420495344275</t>
+          <t>-1124.651344727199</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-36.05</t>
+          <t>-34.84</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-38.60</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>35.9</v>
+        <v>36.03</v>
       </c>
       <c r="AN3" t="n">
-        <v>36.42</v>
+        <v>36.4</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>207.15</t>
+          <t>113.09</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.66</t>
+          <t>-89.77</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>7725.8</v>
+        <v>5058.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>9038.7</t>
+          <t>8187.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>10088.66</v>
+        <v>9806.860000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1312</t>
+          <t>-3129</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-85.55397907369867</t>
+          <t>-256.4565200384027</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-930.0756928206583</t>
+          <t>-1196.420495344275</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-36.05</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-38.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.22000000000001</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>35.77</v>
+        <v>35.9</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.45</v>
+        <v>36.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>518.15</t>
+          <t>207.15</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-96.46</t>
+          <t>-92.66</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>8553.200000000001</v>
+        <v>7725.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>9599.8</t>
+          <t>9038.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10349.7</v>
+        <v>10088.66</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1312</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>67.99542342574854</t>
+          <t>-85.55397907369867</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-497.0804144718968</t>
+          <t>-930.0756928206583</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,12 +2126,12 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-37.94</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.22000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>35.64</v>
+        <v>35.77</v>
       </c>
       <c r="AN5" t="n">
-        <v>36.49</v>
+        <v>36.45</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2018.96</t>
+          <t>518.15</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-96.46</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>10871.8</v>
+        <v>8553.200000000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>9992.1</t>
+          <t>9599.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10687.76</v>
+        <v>10349.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>-1046</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>170.7364848616841</t>
+          <t>67.99542342574854</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>37.6657122574743</t>
+          <t>-497.0804144718968</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-35.36</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>77.87</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>35.51</v>
+        <v>35.64</v>
       </c>
       <c r="AN6" t="n">
-        <v>36.53</v>
+        <v>36.49</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>365.87</t>
+          <t>2018.96</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>11052.4</v>
+        <v>10871.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10895.12</v>
+        <v>10687.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-36.22</t>
+          <t>-35.36</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>95.52</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>35.39</v>
+        <v>35.51</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.59</v>
+        <v>36.53</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>229.08</t>
+          <t>365.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>11317.6</v>
+        <v>11052.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>11140.44</v>
+        <v>10895.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-34.66</t>
+          <t>-36.22</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>35.26</v>
+        <v>35.39</v>
       </c>
       <c r="AN8" t="n">
-        <v>36.64</v>
+        <v>36.59</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>142.57</t>
+          <t>229.08</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-119.03</t>
+          <t>-112.10</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>10351.6</v>
+        <v>11317.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>10788.6</t>
+          <t>12066.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10931.74</v>
+        <v>11140.44</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-437</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>77.1468993095428</t>
+          <t>144.367881711707</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>98.80034504034484</t>
+          <t>514.0832849236103</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-34.66</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-39.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.52</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>35.12</v>
+        <v>35.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>36.71</v>
+        <v>36.64</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>142.57</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-125.82</t>
+          <t>-119.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>10646.4</v>
+        <v>10351.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>11359.5</t>
+          <t>10788.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10960.76</v>
+        <v>10931.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-713</t>
+          <t>-437</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>73.2099091766697</t>
+          <t>77.1468993095428</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>507.1175614556669</t>
+          <t>98.80034504034484</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-39.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>36.48999999999999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>35.01</v>
+        <v>35.12</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.79</v>
+        <v>36.71</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>108.68</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-132.83</t>
+          <t>-125.82</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>9112.4</v>
+        <v>10646.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10143.6</t>
+          <t>11359.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10903.52</v>
+        <v>10960.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1031</t>
+          <t>-713</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-5.682391237693427</t>
+          <t>73.2099091766697</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>171.8879577112803</t>
+          <t>507.1175614556669</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-36.57</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>96.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>36.48999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>34.87</v>
+        <v>35.01</v>
       </c>
       <c r="AN11" t="n">
-        <v>36.86</v>
+        <v>36.79</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>93.73</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-140.53</t>
+          <t>-132.83</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>13322.2</v>
+        <v>9112.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>9983.0</t>
+          <t>10143.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10864.78</v>
+        <v>10903.52</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>-1031</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-37.96790922841592</t>
+          <t>-5.682391237693427</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>504.9925253010406</t>
+          <t>171.8879577112803</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>299.0</t>
+          <t>346.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>39.68</t>
+          <t>33.45</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-38.52</t>
+          <t>-38.69</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>144</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.92</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>92.91</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.91</t>
+          <t>-5.4</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.46</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>34.76</v>
+        <v>34.87</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.94</v>
+        <v>36.86</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>59.14</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-148.06</t>
+          <t>-140.53</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30535.05642857143</t>
+          <t>30503.05848787446</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>12815</v>
+        <v>13322.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9174.3</t>
+          <t>9983.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10767.54</v>
+        <v>10864.78</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-136.6879882337716</t>
+          <t>-37.96790922841592</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>353.4993173828061</t>
+          <t>504.9925253010406</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>10867.0</t>
+          <t>12771.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-35.96</t>
+          <t>-36.14</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.49</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.25</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>35.9</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>381.935</t>
+          <t>406.71</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-26.72</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>74.73</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>18.14</v>
+        <v>18.12</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.82</v>
+        <v>18.78</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-107.83</t>
+          <t>-107.78</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>8737475.800000001</v>
+        <v>7939791.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>13819369.0</t>
+          <t>10834811.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>28136264.12</v>
+        <v>27808635.82</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-5081893</t>
+          <t>-2895019</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-1674567.0666802</t>
+          <t>-1996438.646480869</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3718451.762753243</t>
+          <t>-3766732.335384544</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>811.45</t>
+          <t>381.935</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-59.12</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,68 +6174,68 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.86</v>
+        <v>18.82</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-23.36</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.67</t>
+          <t>-107.83</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>9383601</v>
+        <v>8737475.800000001</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>22951484.1</t>
+          <t>13819369.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>28459246.14</v>
+        <v>28136264.12</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-13567883</t>
+          <t>-5081893</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-1302951.667394193</t>
+          <t>-1674567.0666802</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3461630.774610199</t>
+          <t>-3718451.762753243</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,17 +6361,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>18.05</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>17.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>356.458</t>
+          <t>811.45</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-74.28</t>
+          <t>-59.12</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-3.47</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
           <t>-0.40</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-3.65</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>18.2</v>
+        <v>18.15</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.89</v>
+        <v>18.86</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t>-23.36</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.22</t>
+          <t>-107.67</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>8255008</v>
+        <v>9383601</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>32097739.0</t>
+          <t>22951484.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>29138835.12</v>
+        <v>28459246.14</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-23842731</t>
+          <t>-13567883</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-910464.5569912827</t>
+          <t>-1302951.667394193</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3790149.763884058</t>
+          <t>-3461630.774610199</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>271.149</t>
+          <t>356.458</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-74.28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>18.28</v>
+        <v>18.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.94</v>
+        <v>18.89</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-49.07</t>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-106.47</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>10682520.2</v>
+        <v>8255008</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>33411908.2</t>
+          <t>32097739.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>29853194.9</v>
+        <v>29138835.12</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-22729388</t>
+          <t>-23842731</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-386885.4284653235</t>
+          <t>-910464.5569912827</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3236041.185565136</t>
+          <t>-3790149.763884058</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>653.213</t>
+          <t>271.149</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-58.91</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>18.38</v>
+        <v>18.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.99</v>
+        <v>18.94</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-49.07</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>13729831</v>
+        <v>10682520.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>33416468.7</t>
+          <t>33411908.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>30387285.76</v>
+        <v>29853194.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-19686637</t>
+          <t>-22729388</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>131142.8910073697</t>
+          <t>-386885.4284653235</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-2168665.852767922</t>
+          <t>-3236041.185565136</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>561.188</t>
+          <t>653.213</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-42.19</t>
+          <t>-58.91</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>18.48</v>
+        <v>18.38</v>
       </c>
       <c r="AN18" t="n">
-        <v>19.03</v>
+        <v>18.99</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-34.45</t>
+          <t>-49.91</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-104.97</t>
+          <t>-105.68</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>18901262.2</v>
+        <v>13729831</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>32696459.8</t>
+          <t>33416468.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>30485616.64</v>
+        <v>30387285.76</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-13795197</t>
+          <t>-19686637</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>549289.9353301501</t>
+          <t>131142.8910073697</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1278011.204030193</t>
+          <t>-2168665.852767922</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>507.54</t>
+          <t>561.188</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>-42.19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>18.55</v>
+        <v>18.48</v>
       </c>
       <c r="AN19" t="n">
-        <v>19.06</v>
+        <v>19.03</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-34.45</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.97</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>36519367.2</v>
+        <v>18901262.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>32540510.3</t>
+          <t>32696459.8</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>30733036.4</v>
+        <v>30485616.64</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>3978856</t>
+          <t>-13795197</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>881526.5061229398</t>
+          <t>549289.9353301501</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>176235.0514533557</t>
+          <t>-1278011.204030193</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1035.185</t>
+          <t>507.54</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,58 +8769,58 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>18.63</v>
+        <v>18.55</v>
       </c>
       <c r="AN20" t="n">
-        <v>19.1</v>
+        <v>19.06</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-38.61</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.10</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>55940470</v>
+        <v>36519367.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>32435951.2</t>
+          <t>32540510.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>31266005</v>
+        <v>30733036.4</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>23504518</t>
+          <t>3978856</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1009761.316062864</t>
+          <t>881526.5061229398</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>2379141.700306527</t>
+          <t>176235.0514533557</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1070.149</t>
+          <t>1035.185</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,68 +9184,68 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>18.69</v>
+        <v>18.63</v>
       </c>
       <c r="AN21" t="n">
-        <v>19.16</v>
+        <v>19.1</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.10</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>56141296.2</v>
+        <v>55940470</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>31853386.5</t>
+          <t>32435951.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>31581240.88</v>
+        <v>31266005</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>24287909</t>
+          <t>23504518</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>760783.064382198</t>
+          <t>1009761.316062864</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>4424184.423657246</t>
+          <t>2379141.700306527</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1899.74</t>
+          <t>1070.149</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
           <t>59.09</t>
         </is>
       </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>86.36</t>
-        </is>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.18</v>
+        <v>19.16</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-104.55</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>53103106.4</v>
+        <v>56141296.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>30684373.7</t>
+          <t>31853386.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>31832273.68</v>
+        <v>31581240.88</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>22418732</t>
+          <t>24287909</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>94710.08996855281</t>
+          <t>760783.064382198</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>7015851.227599084</t>
+          <t>4424184.423657246</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4856.308</t>
+          <t>1899.74</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.8</t>
+          <t>-5.82</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>73.06</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>13.41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>407</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>18.77</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>18.73</v>
+        <v>18.74</v>
       </c>
       <c r="AN23" t="n">
-        <v>19.2</v>
+        <v>19.18</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.74</t>
+          <t>18.78</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>80.63</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-105.46</t>
+          <t>-104.55</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/12</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>68743806.22285715</t>
+          <t>68661529.82952926</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>46491657.4</v>
+        <v>53103106.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>28068835.8</t>
+          <t>30684373.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>31715644.28</v>
+        <v>31832273.68</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>18422821</t>
+          <t>22418732</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1163679.207782453</t>
+          <t>94710.08996855281</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>8618125.01081603</t>
+          <t>7015851.227599084</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>98186083.0</t>
+          <t>37224280.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>18.27</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>148.15</t>
+          <t>146.62</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>19.55</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>19.7</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>19.1</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-48.33</t>
+          <t>-50.78</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>36.18</v>
+        <v>36.37</v>
       </c>
       <c r="AN2" t="n">
         <v>36.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>-83.86</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3849.8</v>
+        <v>3549.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7451.1</t>
+          <t>7210.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9807.120000000001</v>
+        <v>9780.68</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3601</t>
+          <t>-3661</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-390.0249546059099</t>
+          <t>-499.3552163091647</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1124.651344727199</t>
+          <t>-1100.671655677066</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-34.84</t>
+          <t>-34.14</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-38.22</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-38.60</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>36.03</v>
+        <v>36.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>36.4</v>
+        <v>36.38</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>113.09</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-89.77</t>
+          <t>-86.91</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>5058.2</v>
+        <v>3849.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>8187.9</t>
+          <t>7451.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9806.860000000001</v>
+        <v>9807.120000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3129</t>
+          <t>-3601</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-256.4565200384027</t>
+          <t>-390.0249546059099</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1196.420495344275</t>
+          <t>-1124.651344727199</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-36.05</t>
+          <t>-34.84</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-38.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>35.9</v>
+        <v>36.03</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.42</v>
+        <v>36.4</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>207.15</t>
+          <t>113.09</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.66</t>
+          <t>-89.77</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>7725.8</v>
+        <v>5058.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>9038.7</t>
+          <t>8187.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>10088.66</v>
+        <v>9806.860000000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1312</t>
+          <t>-3129</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-85.55397907369867</t>
+          <t>-256.4565200384027</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-930.0756928206583</t>
+          <t>-1196.420495344275</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-36.05</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-38.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.22000000000001</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>35.77</v>
+        <v>35.9</v>
       </c>
       <c r="AN5" t="n">
-        <v>36.45</v>
+        <v>36.42</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>518.15</t>
+          <t>207.15</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-96.46</t>
+          <t>-92.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>8553.200000000001</v>
+        <v>7725.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>9599.8</t>
+          <t>9038.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10349.7</v>
+        <v>10088.66</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1312</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>67.99542342574854</t>
+          <t>-85.55397907369867</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-497.0804144718968</t>
+          <t>-930.0756928206583</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-37.94</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.22000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>35.64</v>
+        <v>35.77</v>
       </c>
       <c r="AN6" t="n">
-        <v>36.49</v>
+        <v>36.45</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2018.96</t>
+          <t>518.15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-96.46</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>10871.8</v>
+        <v>8553.200000000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>9992.1</t>
+          <t>9599.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10687.76</v>
+        <v>10349.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>-1046</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>170.7364848616841</t>
+          <t>67.99542342574854</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>37.6657122574743</t>
+          <t>-497.0804144718968</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-35.36</t>
+          <t>-35.53</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>77.87</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>35.51</v>
+        <v>35.64</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.53</v>
+        <v>36.49</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>365.87</t>
+          <t>2018.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>11052.4</v>
+        <v>10871.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10895.12</v>
+        <v>10687.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-36.22</t>
+          <t>-35.36</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>95.52</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>35.39</v>
+        <v>35.51</v>
       </c>
       <c r="AN8" t="n">
-        <v>36.59</v>
+        <v>36.53</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>229.08</t>
+          <t>365.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>11317.6</v>
+        <v>11052.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>11140.44</v>
+        <v>10895.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-34.66</t>
+          <t>-36.22</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>35.26</v>
+        <v>35.39</v>
       </c>
       <c r="AN9" t="n">
-        <v>36.64</v>
+        <v>36.59</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>142.57</t>
+          <t>229.08</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-119.03</t>
+          <t>-112.10</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>10351.6</v>
+        <v>11317.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>10788.6</t>
+          <t>12066.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10931.74</v>
+        <v>11140.44</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-437</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>77.1468993095428</t>
+          <t>144.367881711707</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>98.80034504034484</t>
+          <t>514.0832849236103</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-34.66</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-39.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.52</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>35.12</v>
+        <v>35.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.71</v>
+        <v>36.64</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>142.57</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-125.82</t>
+          <t>-119.03</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>10646.4</v>
+        <v>10351.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>11359.5</t>
+          <t>10788.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10960.76</v>
+        <v>10931.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-713</t>
+          <t>-437</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>73.2099091766697</t>
+          <t>77.1468993095428</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>507.1175614556669</t>
+          <t>98.80034504034484</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>-35.70</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-39.10</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>36.48999999999999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>35.01</v>
+        <v>35.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>36.79</v>
+        <v>36.71</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>108.68</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-132.83</t>
+          <t>-125.82</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>9112.4</v>
+        <v>10646.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10143.6</t>
+          <t>11359.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10903.52</v>
+        <v>10960.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1031</t>
+          <t>-713</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-5.682391237693427</t>
+          <t>73.2099091766697</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>171.8879577112803</t>
+          <t>507.1175614556669</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-36.57</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>346.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33.45</t>
+          <t>-10.17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-38.69</t>
+          <t>-38.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>96.92</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>98.97</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-5.4</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-6.40</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>36.48999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>34.87</v>
+        <v>35.01</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.86</v>
+        <v>36.79</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>93.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-140.53</t>
+          <t>-132.83</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30503.05848787446</t>
+          <t>30469.60256410256</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>13322.2</v>
+        <v>9112.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>9983.0</t>
+          <t>10143.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10864.78</v>
+        <v>10903.52</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>-1031</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-37.96790922841592</t>
+          <t>-5.682391237693427</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>504.9925253010406</t>
+          <t>171.8879577112803</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>12771.0</t>
+          <t>7084.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-36.14</t>
+          <t>-35.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>49.63</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>377.614</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>17.85</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>406.71</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-26.72</t>
+          <t>-12.27</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,75 +5744,75 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>87.83</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>18.12</v>
+        <v>18.08</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.78</v>
+        <v>18.75</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>-0.30</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
       <c r="AS13" t="inlineStr">
         <is>
           <t>3.98</t>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-107.78</t>
+          <t>-107.66</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>7939791.6</v>
+        <v>8347899.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>10834811.3</t>
+          <t>9515210.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>27808635.82</v>
+        <v>27422411.38</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2895019</t>
+          <t>-1167310</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-1996438.646480869</t>
+          <t>-2266574.54745948</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3766732.335384544</t>
+          <t>-3752322.002841841</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>381.935</t>
+          <t>406.71</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-26.72</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,68 +6174,68 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>74.73</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>18.14</v>
+        <v>18.12</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.82</v>
+        <v>18.78</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.83</t>
+          <t>-107.78</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>8737475.800000001</v>
+        <v>7939791.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>13819369.0</t>
+          <t>10834811.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>28136264.12</v>
+        <v>27808635.82</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-5081893</t>
+          <t>-2895019</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-1674567.0666802</t>
+          <t>-1996438.646480869</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3718451.762753243</t>
+          <t>-3766732.335384544</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>811.45</t>
+          <t>381.935</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-59.12</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,68 +6604,68 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.86</v>
+        <v>18.82</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-23.36</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.67</t>
+          <t>-107.83</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>9383601</v>
+        <v>8737475.800000001</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>22951484.1</t>
+          <t>13819369.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>28459246.14</v>
+        <v>28136264.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-13567883</t>
+          <t>-5081893</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1302951.667394193</t>
+          <t>-1674567.0666802</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3461630.774610199</t>
+          <t>-3718451.762753243</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>18.05</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>17.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>356.458</t>
+          <t>811.45</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-74.28</t>
+          <t>-59.12</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-3.47</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
           <t>-0.40</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>-3.65</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>18.2</v>
+        <v>18.15</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.89</v>
+        <v>18.86</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t>-23.36</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.22</t>
+          <t>-107.67</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>8255008</v>
+        <v>9383601</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>32097739.0</t>
+          <t>22951484.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>29138835.12</v>
+        <v>28459246.14</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-23842731</t>
+          <t>-13567883</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-910464.5569912827</t>
+          <t>-1302951.667394193</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3790149.763884058</t>
+          <t>-3461630.774610199</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>271.149</t>
+          <t>356.458</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-74.28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>18.28</v>
+        <v>18.2</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.94</v>
+        <v>18.89</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-49.07</t>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-106.47</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>10682520.2</v>
+        <v>8255008</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>33411908.2</t>
+          <t>32097739.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>29853194.9</v>
+        <v>29138835.12</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-22729388</t>
+          <t>-23842731</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-386885.4284653235</t>
+          <t>-910464.5569912827</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3236041.185565136</t>
+          <t>-3790149.763884058</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>653.213</t>
+          <t>271.149</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-58.91</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>18.38</v>
+        <v>18.28</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.99</v>
+        <v>18.94</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-49.07</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>13729831</v>
+        <v>10682520.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33416468.7</t>
+          <t>33411908.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>30387285.76</v>
+        <v>29853194.9</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-19686637</t>
+          <t>-22729388</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>131142.8910073697</t>
+          <t>-386885.4284653235</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-2168665.852767922</t>
+          <t>-3236041.185565136</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>561.188</t>
+          <t>653.213</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-42.19</t>
+          <t>-58.91</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>18.48</v>
+        <v>18.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>19.03</v>
+        <v>18.99</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-34.45</t>
+          <t>-49.91</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-104.97</t>
+          <t>-105.68</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>18901262.2</v>
+        <v>13729831</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>32696459.8</t>
+          <t>33416468.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>30485616.64</v>
+        <v>30387285.76</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-13795197</t>
+          <t>-19686637</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>549289.9353301501</t>
+          <t>131142.8910073697</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1278011.204030193</t>
+          <t>-2168665.852767922</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8516,17 +8516,17 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>507.54</t>
+          <t>561.188</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>-42.19</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>18.55</v>
+        <v>18.48</v>
       </c>
       <c r="AN20" t="n">
-        <v>19.06</v>
+        <v>19.03</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-34.45</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.97</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>36519367.2</v>
+        <v>18901262.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>32540510.3</t>
+          <t>32696459.8</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>30733036.4</v>
+        <v>30485616.64</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>3978856</t>
+          <t>-13795197</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>881526.5061229398</t>
+          <t>549289.9353301501</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>176235.0514533557</t>
+          <t>-1278011.204030193</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1035.185</t>
+          <t>507.54</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>18.63</v>
+        <v>18.55</v>
       </c>
       <c r="AN21" t="n">
-        <v>19.1</v>
+        <v>19.06</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-38.61</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.10</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>55940470</v>
+        <v>36519367.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>32435951.2</t>
+          <t>32540510.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>31266005</v>
+        <v>30733036.4</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>23504518</t>
+          <t>3978856</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1009761.316062864</t>
+          <t>881526.5061229398</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>2379141.700306527</t>
+          <t>176235.0514533557</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1070.149</t>
+          <t>1035.185</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,68 +9614,68 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>18.69</v>
+        <v>18.63</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.16</v>
+        <v>19.1</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.10</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>56141296.2</v>
+        <v>55940470</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>31853386.5</t>
+          <t>32435951.2</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>31581240.88</v>
+        <v>31266005</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>24287909</t>
+          <t>23504518</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>760783.064382198</t>
+          <t>1009761.316062864</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4424184.423657246</t>
+          <t>2379141.700306527</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1899.74</t>
+          <t>1070.149</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>73.06</t>
+          <t>76.25</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13.41</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>378</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
+          <t>18.18</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
           <t>59.09</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>86.36</t>
-        </is>
-      </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>-4.76</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>19.03</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>18.74</v>
+        <v>18.69</v>
       </c>
       <c r="AN23" t="n">
-        <v>19.18</v>
+        <v>19.16</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.78</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>80.63</t>
+          <t>48.62</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-104.55</t>
+          <t>-104.05</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>68661529.82952926</t>
+          <t>68578178.39529914</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>53103106.4</v>
+        <v>56141296.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>30684373.7</t>
+          <t>31853386.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>31832273.68</v>
+        <v>31581240.88</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>22418732</t>
+          <t>24287909</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>94710.08996855281</t>
+          <t>760783.064382198</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>7015851.227599084</t>
+          <t>4424184.423657246</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>37224280.0</t>
+          <t>19961895.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>18.27</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>106.18</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>146.62</t>
+          <t>143.51</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>19.55</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.35</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>19.1</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-50.78</t>
+          <t>-38.91</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-36.69</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,22 +993,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>36.37</v>
+        <v>36.55</v>
       </c>
       <c r="AN2" t="n">
         <v>36.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>63.23</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-83.86</t>
+          <t>-80.83</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4678.0</t>
+          <t>4189.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3549.2</v>
+        <v>3761.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>7210.5</t>
+          <t>6157.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9780.68</v>
+        <v>9610.879999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3661</t>
+          <t>-2395</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-499.3552163091647</t>
+          <t>-590.6919648693004</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1100.671655677066</t>
+          <t>-1093.044081950046</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4678.0</t>
+          <t>4189.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-34.14</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-48.33</t>
+          <t>-50.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1454,63 +1454,63 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>36.18</v>
+        <v>36.37</v>
       </c>
       <c r="AN3" t="n">
         <v>36.38</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>-83.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3849.8</v>
+        <v>3549.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7451.1</t>
+          <t>7210.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9807.120000000001</v>
+        <v>9780.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3601</t>
+          <t>-3661</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-390.0249546059099</t>
+          <t>-499.3552163091647</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1124.651344727199</t>
+          <t>-1100.671655677066</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-34.84</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.22</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-38.60</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1884,63 +1884,63 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>36.03</v>
+        <v>36.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.4</v>
+        <v>36.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>113.09</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-89.77</t>
+          <t>-86.91</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>5058.2</v>
+        <v>3849.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>8187.9</t>
+          <t>7451.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9806.860000000001</v>
+        <v>9807.120000000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3129</t>
+          <t>-3601</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-256.4565200384027</t>
+          <t>-390.0249546059099</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1196.420495344275</t>
+          <t>-1124.651344727199</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-36.05</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-38.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>35.9</v>
+        <v>36.03</v>
       </c>
       <c r="AN5" t="n">
-        <v>36.42</v>
+        <v>36.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>207.15</t>
+          <t>113.09</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-92.66</t>
+          <t>-89.77</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>7725.8</v>
+        <v>5058.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>9038.7</t>
+          <t>8187.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>10088.66</v>
+        <v>9806.860000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1312</t>
+          <t>-3129</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-85.55397907369867</t>
+          <t>-256.4565200384027</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-930.0756928206583</t>
+          <t>-1196.420495344275</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-38.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.22000000000001</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>35.77</v>
+        <v>35.9</v>
       </c>
       <c r="AN6" t="n">
-        <v>36.45</v>
+        <v>36.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>518.15</t>
+          <t>207.15</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-96.46</t>
+          <t>-92.66</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>8553.200000000001</v>
+        <v>7725.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>9599.8</t>
+          <t>9038.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10349.7</v>
+        <v>10088.66</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1312</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>67.99542342574854</t>
+          <t>-85.55397907369867</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-497.0804144718968</t>
+          <t>-930.0756928206583</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-35.53</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-37.94</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3174,63 +3174,63 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.22000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>35.64</v>
+        <v>35.77</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.49</v>
+        <v>36.45</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2018.96</t>
+          <t>518.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-96.46</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>10871.8</v>
+        <v>8553.200000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9992.1</t>
+          <t>9599.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10687.76</v>
+        <v>10349.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>-1046</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>170.7364848616841</t>
+          <t>67.99542342574854</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>37.6657122574743</t>
+          <t>-497.0804144718968</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-35.36</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3604,63 +3604,63 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>77.87</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>35.51</v>
+        <v>35.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>36.53</v>
+        <v>36.49</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>365.87</t>
+          <t>2018.96</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>11052.4</v>
+        <v>10871.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10895.12</v>
+        <v>10687.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3726,17 +3726,17 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-36.22</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4034,63 +4034,63 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>95.52</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>35.39</v>
+        <v>35.51</v>
       </c>
       <c r="AN9" t="n">
-        <v>36.59</v>
+        <v>36.53</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>229.08</t>
+          <t>365.87</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>11317.6</v>
+        <v>11052.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>11140.44</v>
+        <v>10895.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4156,17 +4156,17 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-34.66</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>35.26</v>
+        <v>35.39</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.64</v>
+        <v>36.59</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>142.57</t>
+          <t>229.08</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-119.03</t>
+          <t>-112.10</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>10351.6</v>
+        <v>11317.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>10788.6</t>
+          <t>12066.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10931.74</v>
+        <v>11140.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-437</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>77.1468993095428</t>
+          <t>144.367881711707</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>98.80034504034484</t>
+          <t>514.0832849236103</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4586,17 +4586,17 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-35.70</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-39.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4894,63 +4894,63 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.52</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>35.12</v>
+        <v>35.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>36.71</v>
+        <v>36.64</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>142.57</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-125.82</t>
+          <t>-119.03</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>10646.4</v>
+        <v>10351.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11359.5</t>
+          <t>10788.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10960.76</v>
+        <v>10931.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-713</t>
+          <t>-437</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>73.2099091766697</t>
+          <t>77.1468993095428</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>507.1175614556669</t>
+          <t>98.80034504034484</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5016,17 +5016,17 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-36.57</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>398.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-10.17</t>
+          <t>-6.28</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-38.35</t>
+          <t>-39.10</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,63 +5324,63 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>98.97</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-6.34</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>36.48999999999999</t>
+          <t>36.69</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>35.01</v>
+        <v>35.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.79</v>
+        <v>36.71</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>39.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>93.73</t>
+          <t>108.68</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-132.83</t>
+          <t>-125.82</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30469.60256410256</t>
+          <t>30435.19843527739</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>9112.4</v>
+        <v>10646.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>10143.6</t>
+          <t>11359.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10903.52</v>
+        <v>10960.76</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1031</t>
+          <t>-713</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-5.682391237693427</t>
+          <t>73.2099091766697</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>171.8879577112803</t>
+          <t>507.1175614556669</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>7084.0</t>
+          <t>14720.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5446,17 +5446,17 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/02/07</t>
+          <t>2025/12/02</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-35.79</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>377.614</t>
+          <t>361.704</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>87.83</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AM13" t="n">
         <v>18.08</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.75</v>
+        <v>18.72</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-107.66</t>
+          <t>-107.47</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6765882.0</t>
+          <t>6511141.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>8347899.8</v>
+        <v>8405984.800000001</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>9515210.0</t>
+          <t>8330496.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>27422411.38</v>
+        <v>26697893.5</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1167310</t>
+          <t>75488</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-2266574.54745948</t>
+          <t>-2482106.508618161</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3752322.002841841</t>
+          <t>-3667532.294990905</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>6765882.0</t>
+          <t>6511141.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>406.71</t>
+          <t>377.614</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-26.72</t>
+          <t>-12.27</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,75 +6174,75 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>87.83</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>18.12</v>
+        <v>18.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.78</v>
+        <v>18.75</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
           <t>-0.30</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
       <c r="AS14" t="inlineStr">
         <is>
           <t>3.98</t>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.78</t>
+          <t>-107.66</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>7939791.6</v>
+        <v>8347899.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>10834811.3</t>
+          <t>9515210.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>27808635.82</v>
+        <v>27422411.38</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2895019</t>
+          <t>-1167310</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-1996438.646480869</t>
+          <t>-2266574.54745948</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3766732.335384544</t>
+          <t>-3752322.002841841</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>381.935</t>
+          <t>406.71</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-26.72</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,68 +6604,68 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>74.73</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>18.14</v>
+        <v>18.12</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.82</v>
+        <v>18.78</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.83</t>
+          <t>-107.78</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>8737475.800000001</v>
+        <v>7939791.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>13819369.0</t>
+          <t>10834811.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>28136264.12</v>
+        <v>27808635.82</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-5081893</t>
+          <t>-2895019</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1674567.0666802</t>
+          <t>-1996438.646480869</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3718451.762753243</t>
+          <t>-3766732.335384544</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>811.45</t>
+          <t>381.935</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-59.12</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,68 +7034,68 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.86</v>
+        <v>18.82</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-23.36</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.67</t>
+          <t>-107.83</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>9383601</v>
+        <v>8737475.800000001</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>22951484.1</t>
+          <t>13819369.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>28459246.14</v>
+        <v>28136264.12</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-13567883</t>
+          <t>-5081893</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-1302951.667394193</t>
+          <t>-1674567.0666802</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3461630.774610199</t>
+          <t>-3718451.762753243</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>18.05</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>17.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>356.458</t>
+          <t>811.45</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-74.28</t>
+          <t>-59.12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-3.47</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
           <t>-0.40</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>-3.65</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>18.2</v>
+        <v>18.15</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.89</v>
+        <v>18.86</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t>-23.36</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.22</t>
+          <t>-107.67</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>8255008</v>
+        <v>9383601</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>32097739.0</t>
+          <t>22951484.1</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>29138835.12</v>
+        <v>28459246.14</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-23842731</t>
+          <t>-13567883</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-910464.5569912827</t>
+          <t>-1302951.667394193</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3790149.763884058</t>
+          <t>-3461630.774610199</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>271.149</t>
+          <t>356.458</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-74.28</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>18.28</v>
+        <v>18.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.94</v>
+        <v>18.89</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-49.07</t>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-106.47</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>10682520.2</v>
+        <v>8255008</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>33411908.2</t>
+          <t>32097739.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>29853194.9</v>
+        <v>29138835.12</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-22729388</t>
+          <t>-23842731</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-386885.4284653235</t>
+          <t>-910464.5569912827</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3236041.185565136</t>
+          <t>-3790149.763884058</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>653.213</t>
+          <t>271.149</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-58.91</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>18.38</v>
+        <v>18.28</v>
       </c>
       <c r="AN19" t="n">
-        <v>18.99</v>
+        <v>18.94</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-49.07</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>13729831</v>
+        <v>10682520.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>33416468.7</t>
+          <t>33411908.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>30387285.76</v>
+        <v>29853194.9</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-19686637</t>
+          <t>-22729388</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>131142.8910073697</t>
+          <t>-386885.4284653235</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-2168665.852767922</t>
+          <t>-3236041.185565136</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>561.188</t>
+          <t>653.213</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-42.19</t>
+          <t>-58.91</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,17 +8754,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>18.48</v>
+        <v>18.38</v>
       </c>
       <c r="AN20" t="n">
-        <v>19.03</v>
+        <v>18.99</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-34.45</t>
+          <t>-49.91</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-104.97</t>
+          <t>-105.68</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>18901262.2</v>
+        <v>13729831</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>32696459.8</t>
+          <t>33416468.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>30485616.64</v>
+        <v>30387285.76</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-13795197</t>
+          <t>-19686637</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>549289.9353301501</t>
+          <t>131142.8910073697</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1278011.204030193</t>
+          <t>-2168665.852767922</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>507.54</t>
+          <t>561.188</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>-42.19</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>18.55</v>
+        <v>18.48</v>
       </c>
       <c r="AN21" t="n">
-        <v>19.06</v>
+        <v>19.03</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-34.45</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.97</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>36519367.2</v>
+        <v>18901262.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>32540510.3</t>
+          <t>32696459.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>30733036.4</v>
+        <v>30485616.64</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>3978856</t>
+          <t>-13795197</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>881526.5061229398</t>
+          <t>549289.9353301501</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>176235.0514533557</t>
+          <t>-1278011.204030193</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1035.185</t>
+          <t>507.54</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>18.63</v>
+        <v>18.55</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.1</v>
+        <v>19.06</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-38.61</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-104.10</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>55940470</v>
+        <v>36519367.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>32435951.2</t>
+          <t>32540510.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>31266005</v>
+        <v>30733036.4</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>23504518</t>
+          <t>3978856</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1009761.316062864</t>
+          <t>881526.5061229398</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2379141.700306527</t>
+          <t>176235.0514533557</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9903,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1070.149</t>
+          <t>1035.185</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.25</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,68 +10044,68 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>362</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.76</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>18.69</v>
+        <v>18.63</v>
       </c>
       <c r="AN23" t="n">
-        <v>19.16</v>
+        <v>19.1</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.85</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>-4.88</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-104.05</t>
+          <t>-104.10</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>68578178.39529914</t>
+          <t>68494520.54765292</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>56141296.2</v>
+        <v>55940470</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>31853386.5</t>
+          <t>32435951.2</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>31581240.88</v>
+        <v>31266005</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>24287909</t>
+          <t>23504518</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>760783.064382198</t>
+          <t>1009761.316062864</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>4424184.423657246</t>
+          <t>2379141.700306527</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>19961895.0</t>
+          <t>18358277.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>105.29</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>143.51</t>
+          <t>142.99</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>19.35</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-38.91</t>
+          <t>-27.28</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-36.69</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>36.55</v>
+        <v>36.74</v>
       </c>
       <c r="AN2" t="n">
         <v>36.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>47.16</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-80.83</t>
+          <t>-78.27</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>4189.0</t>
+          <t>5442.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3761.6</v>
+        <v>4414.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6157.4</t>
+          <t>6070.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9610.879999999999</v>
+        <v>9569.120000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2395</t>
+          <t>-1655</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-590.6919648693004</t>
+          <t>-648.4937669343898</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1093.044081950046</t>
+          <t>-966.4036782923813</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>4189.0</t>
+          <t>5442.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-50.78</t>
+          <t>-38.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-36.69</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,33 +1423,33 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>36.37</v>
+        <v>36.55</v>
       </c>
       <c r="AN3" t="n">
         <v>36.38</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>63.23</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-83.86</t>
+          <t>-80.83</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4678.0</t>
+          <t>4189.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3549.2</v>
+        <v>3761.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>7210.5</t>
+          <t>6157.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9780.68</v>
+        <v>9610.879999999999</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3661</t>
+          <t>-2395</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-499.3552163091647</t>
+          <t>-590.6919648693004</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1100.671655677066</t>
+          <t>-1093.044081950046</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4678.0</t>
+          <t>4189.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-48.33</t>
+          <t>-50.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>36.18</v>
+        <v>36.37</v>
       </c>
       <c r="AN4" t="n">
         <v>36.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>-83.86</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3849.8</v>
+        <v>3549.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7451.1</t>
+          <t>7210.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9807.120000000001</v>
+        <v>9780.68</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3601</t>
+          <t>-3661</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-390.0249546059099</t>
+          <t>-499.3552163091647</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1124.651344727199</t>
+          <t>-1100.671655677066</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-38.22</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-38.60</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>36.03</v>
+        <v>36.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>36.4</v>
+        <v>36.38</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>113.09</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-89.77</t>
+          <t>-86.91</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>5058.2</v>
+        <v>3849.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>8187.9</t>
+          <t>7451.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>9806.860000000001</v>
+        <v>9807.120000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3129</t>
+          <t>-3601</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-256.4565200384027</t>
+          <t>-390.0249546059099</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1196.420495344275</t>
+          <t>-1124.651344727199</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-38.60</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>35.9</v>
+        <v>36.03</v>
       </c>
       <c r="AN6" t="n">
-        <v>36.42</v>
+        <v>36.4</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>207.15</t>
+          <t>113.09</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-92.66</t>
+          <t>-89.77</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>7725.8</v>
+        <v>5058.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>9038.7</t>
+          <t>8187.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>10088.66</v>
+        <v>9806.860000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1312</t>
+          <t>-3129</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-85.55397907369867</t>
+          <t>-256.4565200384027</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-930.0756928206583</t>
+          <t>-1196.420495344275</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-38.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.22000000000001</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>35.77</v>
+        <v>35.9</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.45</v>
+        <v>36.42</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>518.15</t>
+          <t>207.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-96.46</t>
+          <t>-92.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>8553.200000000001</v>
+        <v>7725.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9599.8</t>
+          <t>9038.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10349.7</v>
+        <v>10088.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1312</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>67.99542342574854</t>
+          <t>-85.55397907369867</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-497.0804144718968</t>
+          <t>-930.0756928206583</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-37.94</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.22000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>35.64</v>
+        <v>35.77</v>
       </c>
       <c r="AN8" t="n">
-        <v>36.49</v>
+        <v>36.45</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2018.96</t>
+          <t>518.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-96.46</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>10871.8</v>
+        <v>8553.200000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>9992.1</t>
+          <t>9599.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10687.76</v>
+        <v>10349.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>-1046</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>170.7364848616841</t>
+          <t>67.99542342574854</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>37.6657122574743</t>
+          <t>-497.0804144718968</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>77.87</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>35.51</v>
+        <v>35.64</v>
       </c>
       <c r="AN9" t="n">
-        <v>36.53</v>
+        <v>36.49</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>365.87</t>
+          <t>2018.96</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>11052.4</v>
+        <v>10871.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10895.12</v>
+        <v>10687.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>95.52</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>35.39</v>
+        <v>35.51</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.59</v>
+        <v>36.53</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>229.08</t>
+          <t>365.87</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>11317.6</v>
+        <v>11052.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>11140.44</v>
+        <v>10895.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>35.26</v>
+        <v>35.39</v>
       </c>
       <c r="AN11" t="n">
-        <v>36.64</v>
+        <v>36.59</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>142.57</t>
+          <t>229.08</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-119.03</t>
+          <t>-112.10</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>10351.6</v>
+        <v>11317.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10788.6</t>
+          <t>12066.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10931.74</v>
+        <v>11140.44</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-437</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>77.1468993095428</t>
+          <t>144.367881711707</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>98.80034504034484</t>
+          <t>514.0832849236103</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>398.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.28</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-39.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.52</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.34</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>36.91</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>35.12</v>
+        <v>35.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.71</v>
+        <v>36.64</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>108.68</t>
+          <t>142.57</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.82</t>
+          <t>-119.03</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30435.19843527739</t>
+          <t>30403.56178977273</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>10646.4</v>
+        <v>10351.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>11359.5</t>
+          <t>10788.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10960.76</v>
+        <v>10931.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-713</t>
+          <t>-437</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>73.2099091766697</t>
+          <t>77.1468993095428</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>507.1175614556669</t>
+          <t>98.80034504034484</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>14720.0</t>
+          <t>6316.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>11.53</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>361.704</t>
+          <t>494.137</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-12.58</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,7 +5759,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -5769,17 +5769,17 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -5791,26 +5791,26 @@
         <v>18.08</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.72</v>
+        <v>18.68</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-107.47</t>
+          <t>-107.23</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>6511141.0</t>
+          <t>8912758.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>8405984.800000001</v>
+        <v>7286683.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8330496.4</t>
+          <t>8335142.1</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>26697893.5</v>
+        <v>25916531.72</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>-1048458</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-2482106.508618161</t>
+          <t>-2613531.648387747</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3667532.294990905</t>
+          <t>-3336369.917120475</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>6511141.0</t>
+          <t>8912758.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>377.614</t>
+          <t>361.704</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,68 +6174,68 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>87.83</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AM14" t="n">
         <v>18.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.75</v>
+        <v>18.72</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.66</t>
+          <t>-107.47</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>6765882.0</t>
+          <t>6511141.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>8347899.8</v>
+        <v>8405984.800000001</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>9515210.0</t>
+          <t>8330496.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>27422411.38</v>
+        <v>26697893.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1167310</t>
+          <t>75488</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-2266574.54745948</t>
+          <t>-2482106.508618161</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3752322.002841841</t>
+          <t>-3667532.294990905</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>6765882.0</t>
+          <t>6511141.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>406.71</t>
+          <t>377.614</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-26.72</t>
+          <t>-12.27</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,75 +6604,75 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>87.83</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>18.12</v>
+        <v>18.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.78</v>
+        <v>18.75</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>-0.30</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
       <c r="AS15" t="inlineStr">
         <is>
           <t>3.98</t>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.78</t>
+          <t>-107.66</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>7939791.6</v>
+        <v>8347899.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>10834811.3</t>
+          <t>9515210.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>27808635.82</v>
+        <v>27422411.38</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2895019</t>
+          <t>-1167310</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-1996438.646480869</t>
+          <t>-2266574.54745948</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3766732.335384544</t>
+          <t>-3752322.002841841</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>381.935</t>
+          <t>406.71</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-26.72</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,68 +7034,68 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>74.73</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>18.14</v>
+        <v>18.12</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.82</v>
+        <v>18.78</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.83</t>
+          <t>-107.78</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>8737475.800000001</v>
+        <v>7939791.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>13819369.0</t>
+          <t>10834811.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>28136264.12</v>
+        <v>27808635.82</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-5081893</t>
+          <t>-2895019</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-1674567.0666802</t>
+          <t>-1996438.646480869</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3718451.762753243</t>
+          <t>-3766732.335384544</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>811.45</t>
+          <t>381.935</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-59.12</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,68 +7464,68 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.86</v>
+        <v>18.82</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-23.36</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.67</t>
+          <t>-107.83</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>9383601</v>
+        <v>8737475.800000001</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>22951484.1</t>
+          <t>13819369.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>28459246.14</v>
+        <v>28136264.12</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-13567883</t>
+          <t>-5081893</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-1302951.667394193</t>
+          <t>-1674567.0666802</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3461630.774610199</t>
+          <t>-3718451.762753243</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
           <t>18.05</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>17.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>356.458</t>
+          <t>811.45</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-74.28</t>
+          <t>-59.12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-3.47</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
           <t>-0.40</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>-3.65</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>18.2</v>
+        <v>18.15</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.89</v>
+        <v>18.86</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t>-23.36</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-107.22</t>
+          <t>-107.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>8255008</v>
+        <v>9383601</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>32097739.0</t>
+          <t>22951484.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>29138835.12</v>
+        <v>28459246.14</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-23842731</t>
+          <t>-13567883</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-910464.5569912827</t>
+          <t>-1302951.667394193</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3790149.763884058</t>
+          <t>-3461630.774610199</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>271.149</t>
+          <t>356.458</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-74.28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>18.28</v>
+        <v>18.2</v>
       </c>
       <c r="AN19" t="n">
-        <v>18.94</v>
+        <v>18.89</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-49.07</t>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-106.47</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>10682520.2</v>
+        <v>8255008</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>33411908.2</t>
+          <t>32097739.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>29853194.9</v>
+        <v>29138835.12</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-22729388</t>
+          <t>-23842731</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-386885.4284653235</t>
+          <t>-910464.5569912827</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3236041.185565136</t>
+          <t>-3790149.763884058</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>653.213</t>
+          <t>271.149</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.63</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-58.91</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>18.38</v>
+        <v>18.28</v>
       </c>
       <c r="AN20" t="n">
-        <v>18.99</v>
+        <v>18.94</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-49.07</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>13729831</v>
+        <v>10682520.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>33416468.7</t>
+          <t>33411908.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>30387285.76</v>
+        <v>29853194.9</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-19686637</t>
+          <t>-22729388</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>131142.8910073697</t>
+          <t>-386885.4284653235</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-2168665.852767922</t>
+          <t>-3236041.185565136</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>561.188</t>
+          <t>653.213</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-42.19</t>
+          <t>-58.91</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,17 +9184,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>18.48</v>
+        <v>18.38</v>
       </c>
       <c r="AN21" t="n">
-        <v>19.03</v>
+        <v>18.99</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-34.45</t>
+          <t>-49.91</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-104.97</t>
+          <t>-105.68</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>18901262.2</v>
+        <v>13729831</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>32696459.8</t>
+          <t>33416468.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>30485616.64</v>
+        <v>30387285.76</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-13795197</t>
+          <t>-19686637</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>549289.9353301501</t>
+          <t>131142.8910073697</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1278011.204030193</t>
+          <t>-2168665.852767922</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>507.54</t>
+          <t>561.188</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>-42.19</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>18.55</v>
+        <v>18.48</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.06</v>
+        <v>19.03</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-34.45</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.97</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>36519367.2</v>
+        <v>18901262.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>32540510.3</t>
+          <t>32696459.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>30733036.4</v>
+        <v>30485616.64</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>3978856</t>
+          <t>-13795197</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>881526.5061229398</t>
+          <t>549289.9353301501</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>176235.0514533557</t>
+          <t>-1278011.204030193</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1035.185</t>
+          <t>507.54</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>72.46</t>
+          <t>12.23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.69</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>494</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>18.63</v>
+        <v>18.55</v>
       </c>
       <c r="AN23" t="n">
-        <v>19.1</v>
+        <v>19.06</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.85</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-38.61</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-104.10</t>
+          <t>-104.54</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>68494520.54765292</t>
+          <t>68416217.44602273</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>55940470</v>
+        <v>36519367.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>32435951.2</t>
+          <t>32540510.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>31266005</v>
+        <v>30733036.4</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>23504518</t>
+          <t>3978856</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1009761.316062864</t>
+          <t>881526.5061229398</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2379141.700306527</t>
+          <t>176235.0514533557</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>18358277.0</t>
+          <t>8866301.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>142.99</t>
+          <t>143.33</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -888,7 +888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.28</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-37.10</t>
+          <t>-37.52</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>93.33</t>
+          <t>78.84</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>36.74</v>
+        <v>36.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>36.38</v>
+        <v>36.35</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>31.12</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-78.27</t>
+          <t>-76.43</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5442.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4414.2</v>
+        <v>4552.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>6070.0</t>
+          <t>4805.3</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9569.120000000001</v>
+        <v>9184.860000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1655</t>
+          <t>-252</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-648.4937669343898</t>
+          <t>-707.6478495252077</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-966.4036782923813</t>
+          <t>-1032.995303774706</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5442.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-38.91</t>
+          <t>-27.28</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-36.69</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>96.97</t>
+          <t>93.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>36.55</v>
+        <v>36.74</v>
       </c>
       <c r="AN3" t="n">
         <v>36.38</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>63.23</t>
+          <t>47.16</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-80.83</t>
+          <t>-78.27</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4189.0</t>
+          <t>5442.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3761.6</v>
+        <v>4414.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>6157.4</t>
+          <t>6070.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9610.879999999999</v>
+        <v>9569.120000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2395</t>
+          <t>-1655</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-590.6919648693004</t>
+          <t>-648.4937669343898</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1093.044081950046</t>
+          <t>-966.4036782923813</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4189.0</t>
+          <t>5442.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-50.78</t>
+          <t>-38.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-36.69</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,33 +1853,33 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>96.97</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>36.37</v>
+        <v>36.55</v>
       </c>
       <c r="AN4" t="n">
         <v>36.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>63.23</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-83.86</t>
+          <t>-80.83</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4678.0</t>
+          <t>4189.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3549.2</v>
+        <v>3761.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>7210.5</t>
+          <t>6157.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9780.68</v>
+        <v>9610.879999999999</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-3661</t>
+          <t>-2395</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-499.3552163091647</t>
+          <t>-590.6919648693004</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1100.671655677066</t>
+          <t>-1093.044081950046</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4678.0</t>
+          <t>4189.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-48.33</t>
+          <t>-50.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>36.18</v>
+        <v>36.37</v>
       </c>
       <c r="AN5" t="n">
         <v>36.38</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>-83.86</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3849.8</v>
+        <v>3549.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7451.1</t>
+          <t>7210.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>9807.120000000001</v>
+        <v>9780.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3601</t>
+          <t>-3661</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-390.0249546059099</t>
+          <t>-499.3552163091647</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1124.651344727199</t>
+          <t>-1100.671655677066</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-38.22</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-38.60</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>36.03</v>
+        <v>36.18</v>
       </c>
       <c r="AN6" t="n">
-        <v>36.4</v>
+        <v>36.38</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>113.09</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-89.77</t>
+          <t>-86.91</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>5058.2</v>
+        <v>3849.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>8187.9</t>
+          <t>7451.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>9806.860000000001</v>
+        <v>9807.120000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3129</t>
+          <t>-3601</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-256.4565200384027</t>
+          <t>-390.0249546059099</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1196.420495344275</t>
+          <t>-1124.651344727199</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-38.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>42.42</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>35.9</v>
+        <v>36.03</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.42</v>
+        <v>36.4</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>207.15</t>
+          <t>113.09</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-92.66</t>
+          <t>-89.77</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>7725.8</v>
+        <v>5058.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>9038.7</t>
+          <t>8187.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>10088.66</v>
+        <v>9806.860000000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1312</t>
+          <t>-3129</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-85.55397907369867</t>
+          <t>-256.4565200384027</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-930.0756928206583</t>
+          <t>-1196.420495344275</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-38.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>58.82</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.22000000000001</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>35.77</v>
+        <v>35.9</v>
       </c>
       <c r="AN8" t="n">
-        <v>36.45</v>
+        <v>36.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>518.15</t>
+          <t>207.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-96.46</t>
+          <t>-92.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>8553.200000000001</v>
+        <v>7725.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>9599.8</t>
+          <t>9038.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10349.7</v>
+        <v>10088.66</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1312</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>67.99542342574854</t>
+          <t>-85.55397907369867</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-497.0804144718968</t>
+          <t>-930.0756928206583</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-37.94</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.22000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>35.64</v>
+        <v>35.77</v>
       </c>
       <c r="AN9" t="n">
-        <v>36.49</v>
+        <v>36.45</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2018.96</t>
+          <t>518.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-96.46</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>10871.8</v>
+        <v>8553.200000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>9992.1</t>
+          <t>9599.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10687.76</v>
+        <v>10349.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>-1046</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>170.7364848616841</t>
+          <t>67.99542342574854</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>37.6657122574743</t>
+          <t>-497.0804144718968</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>77.87</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>35.51</v>
+        <v>35.64</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.53</v>
+        <v>36.49</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>365.87</t>
+          <t>2018.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>11052.4</v>
+        <v>10871.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10895.12</v>
+        <v>10687.76</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>95.52</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>35.39</v>
+        <v>35.51</v>
       </c>
       <c r="AN11" t="n">
-        <v>36.59</v>
+        <v>36.53</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>229.08</t>
+          <t>365.87</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>11317.6</v>
+        <v>11052.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>11140.44</v>
+        <v>10895.12</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>414.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-6.20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>35.26</v>
+        <v>35.39</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.64</v>
+        <v>36.59</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>142.57</t>
+          <t>229.08</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-119.03</t>
+          <t>-112.10</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30403.56178977273</t>
+          <t>30366.92553191489</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>10351.6</v>
+        <v>11317.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>10788.6</t>
+          <t>12066.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>10931.74</v>
+        <v>11140.44</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-437</t>
+          <t>-748</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>77.1468993095428</t>
+          <t>144.367881711707</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>98.80034504034484</t>
+          <t>514.0832849236103</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>6316.0</t>
+          <t>15697.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.53</t>
+          <t>11.38</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>321.293</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>17.95</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>494.137</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-12.58</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5749,269 +5749,269 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>84.72</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-0.77</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-3.14</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>17.93</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>17.25</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
           <t>-0.28</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-3.23</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>-1.83</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-106.93</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>68331381.42978723</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>5737884.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>7061273.6</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>7899374.7</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>25505500.48</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-838101</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-2712874.864740888</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-3259262.554683162</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>5737884.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>16.15</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>11.15</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>中釉</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>中釉</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>4.154975628533399</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>16.21035637221673</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>6.111603549217973</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>105.59</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>18.68%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>144.36</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>色釉料76.73%、其他19.26%、玉晶石4.01% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>中釉-玻璃陶瓷-上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
         <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="AM13" t="n">
-        <v>18.08</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>18.68</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>13.40</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-107.23</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>68416217.44602273</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>8912758.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>7286683.2</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>8335142.1</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>25916531.72</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-1048458</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-2613531.648387747</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-3336369.917120475</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>8912758.0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>16.15</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>10.84</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>中釉</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>中釉</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>4.154975628533399</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>16.21035637221673</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>6.111603549217973</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>105.29</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>18.68%</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>143.33</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>2990</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>色釉料76.73%、其他19.26%、玉晶石4.01% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>中釉-玻璃陶瓷-上市</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>18.15</t>
-        </is>
-      </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,42 +6043,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>494.137</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>361.704</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>17.9</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-12.58</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -6199,17 +6199,17 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -6221,26 +6221,26 @@
         <v>18.08</v>
       </c>
       <c r="AN14" t="n">
-        <v>18.72</v>
+        <v>18.68</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-107.47</t>
+          <t>-107.23</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>6511141.0</t>
+          <t>8912758.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>8405984.800000001</v>
+        <v>7286683.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>8330496.4</t>
+          <t>8335142.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>26697893.5</v>
+        <v>25916531.72</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>-1048458</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-2482106.508618161</t>
+          <t>-2613531.648387747</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3667532.294990905</t>
+          <t>-3336369.917120475</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>6511141.0</t>
+          <t>8912758.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>377.614</t>
+          <t>361.704</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6503,12 +6503,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6609,63 +6609,63 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>87.83</t>
+          <t>87.04</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AM15" t="n">
         <v>18.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.75</v>
+        <v>18.72</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>6.12</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.66</t>
+          <t>-107.47</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>6765882.0</t>
+          <t>6511141.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>8347899.8</v>
+        <v>8405984.800000001</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>9515210.0</t>
+          <t>8330496.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>27422411.38</v>
+        <v>26697893.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1167310</t>
+          <t>75488</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-2266574.54745948</t>
+          <t>-2482106.508618161</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3752322.002841841</t>
+          <t>-3667532.294990905</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>6765882.0</t>
+          <t>6511141.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>406.71</t>
+          <t>377.614</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-26.72</t>
+          <t>-12.27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7039,70 +7039,70 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>87.83</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>18.12</v>
+        <v>18.08</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.78</v>
+        <v>18.75</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>-0.30</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>3.98</t>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.78</t>
+          <t>-107.66</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>7939791.6</v>
+        <v>8347899.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>10834811.3</t>
+          <t>9515210.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>27808635.82</v>
+        <v>27422411.38</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2895019</t>
+          <t>-1167310</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-1996438.646480869</t>
+          <t>-2266574.54745948</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3766732.335384544</t>
+          <t>-3752322.002841841</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>381.935</t>
+          <t>406.71</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-26.72</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7469,63 +7469,63 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>43.73</t>
+          <t>74.73</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>18.14</v>
+        <v>18.12</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.82</v>
+        <v>18.78</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.83</t>
+          <t>-107.78</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>8737475.800000001</v>
+        <v>7939791.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>13819369.0</t>
+          <t>10834811.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>28136264.12</v>
+        <v>27808635.82</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-5081893</t>
+          <t>-2895019</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-1674567.0666802</t>
+          <t>-1996438.646480869</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3718451.762753243</t>
+          <t>-3766732.335384544</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>811.45</t>
+          <t>381.935</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-59.12</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7899,63 +7899,63 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>43.73</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.86</v>
+        <v>18.82</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-23.36</t>
+          <t>-8.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-107.67</t>
+          <t>-107.83</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>9383601</v>
+        <v>8737475.800000001</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22951484.1</t>
+          <t>13819369.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>28459246.14</v>
+        <v>28136264.12</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-13567883</t>
+          <t>-5081893</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-1302951.667394193</t>
+          <t>-1674567.0666802</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3461630.774610199</t>
+          <t>-3718451.762753243</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
           <t>18.05</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>17.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>356.458</t>
+          <t>811.45</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-74.28</t>
+          <t>-59.12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8329,68 +8329,68 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-3.47</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
           <t>-0.40</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>-3.65</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>18.2</v>
+        <v>18.15</v>
       </c>
       <c r="AN19" t="n">
-        <v>18.89</v>
+        <v>18.86</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>18.93</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-41.60</t>
+          <t>-23.36</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-107.22</t>
+          <t>-107.67</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>8255008</v>
+        <v>9383601</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>32097739.0</t>
+          <t>22951484.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>29138835.12</v>
+        <v>28459246.14</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-23842731</t>
+          <t>-13567883</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-910464.5569912827</t>
+          <t>-1302951.667394193</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3790149.763884058</t>
+          <t>-3461630.774610199</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>6220716.0</t>
+          <t>14509266.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>17.45</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>271.149</t>
+          <t>356.458</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-68.03</t>
+          <t>-74.28</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>-7.96</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8759,68 +8759,68 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
+          <t>7.02</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
           <t>3.51</t>
         </is>
       </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>8.22</t>
-        </is>
-      </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.47</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>17.42</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>18.28</v>
+        <v>18.2</v>
       </c>
       <c r="AN20" t="n">
-        <v>18.94</v>
+        <v>18.89</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.91</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-49.07</t>
+          <t>-41.60</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-106.47</t>
+          <t>-107.22</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>10682520.2</v>
+        <v>8255008</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>33411908.2</t>
+          <t>32097739.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>29853194.9</v>
+        <v>29138835.12</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-22729388</t>
+          <t>-23842731</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-386885.4284653235</t>
+          <t>-910464.5569912827</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3236041.185565136</t>
+          <t>-3790149.763884058</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>4725341.0</t>
+          <t>6220716.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.45</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>17.25</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>653.213</t>
+          <t>271.149</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-58.91</t>
+          <t>-68.03</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-9.02</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.96</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9189,68 +9189,68 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>7.05</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.47</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>18.38</v>
+        <v>18.28</v>
       </c>
       <c r="AN21" t="n">
-        <v>18.99</v>
+        <v>18.94</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-49.91</t>
+          <t>-49.07</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-105.68</t>
+          <t>-106.47</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>13729831</v>
+        <v>10682520.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>33416468.7</t>
+          <t>33411908.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>30387285.76</v>
+        <v>29853194.9</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-19686637</t>
+          <t>-22729388</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>131142.8910073697</t>
+          <t>-386885.4284653235</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-2168665.852767922</t>
+          <t>-3236041.185565136</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>11367124.0</t>
+          <t>4725341.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>17.25</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>561.188</t>
+          <t>653.213</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-42.19</t>
+          <t>-58.91</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-9.02</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.96</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-4.96</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>21.15</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>18.48</v>
+        <v>18.38</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.03</v>
+        <v>18.99</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-34.45</t>
+          <t>-49.91</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-104.97</t>
+          <t>-105.68</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>18901262.2</v>
+        <v>13729831</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>32696459.8</t>
+          <t>33416468.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>30485616.64</v>
+        <v>30387285.76</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-13795197</t>
+          <t>-19686637</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>549289.9353301501</t>
+          <t>131142.8910073697</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1278011.204030193</t>
+          <t>-2168665.852767922</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>10095558.0</t>
+          <t>11367124.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>6.19</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.75</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.15</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>507.54</t>
+          <t>561.188</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>12.23</t>
+          <t>-42.19</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-7.69</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.96</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10049,68 +10049,68 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>321</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>7.05</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.04</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>18.55</v>
+        <v>18.48</v>
       </c>
       <c r="AN23" t="n">
-        <v>19.06</v>
+        <v>19.03</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-38.61</t>
+          <t>-34.45</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-104.54</t>
+          <t>-104.97</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>68416217.44602273</t>
+          <t>68331381.42978723</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>36519367.2</v>
+        <v>18901262.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>32540510.3</t>
+          <t>32696459.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>30733036.4</v>
+        <v>30485616.64</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>3978856</t>
+          <t>-13795197</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>881526.5061229398</t>
+          <t>549289.9353301501</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>176235.0514533557</t>
+          <t>-1278011.204030193</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>8866301.0</t>
+          <t>10095558.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>105.29</t>
+          <t>105.59</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>143.33</t>
+          <t>144.36</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/個人、民間企業、政府機構.xlsx
+++ b/Result/checksun_type/個人、民間企業、政府機構.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-37.52</t>
+          <t>-38.44</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,95 +993,87 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.52</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.84</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-0.66</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
+          <t>48.41</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.67</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-4.26</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.67999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>36.9</v>
+        <v>37.06</v>
       </c>
       <c r="AN2" t="n">
-        <v>36.35</v>
+        <v>36.31</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>37.88</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>31.12</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.38</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-76.43</t>
+          <t>-75.76</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>5174.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4552.4</v>
+        <v>4506.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4805.3</t>
+          <t>4178.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>9184.860000000001</v>
+        <v>9134.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-252</t>
+          <t>328</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-707.6478495252077</t>
+          <t>-736.3919586779397</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1032.995303774706</t>
+          <t>-894.4845590179657</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>3050.0</t>
+          <t>5174.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1318,7 +1310,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-27.28</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-37.10</t>
+          <t>-37.52</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,74 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>56.52</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>93.33</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
+          <t>78.84</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>2.45</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-4.42</t>
+          <t>-4.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>37.67</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>36.74</v>
+        <v>36.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>36.38</v>
+        <v>36.35</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>38.06</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>47.16</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
+          <t>31.12</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.37</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1520,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-78.27</t>
+          <t>-76.43</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5442.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4414.2</v>
+        <v>4552.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>6070.0</t>
+          <t>4805.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>9569.120000000001</v>
+        <v>9184.860000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1655</t>
+          <t>-252</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-648.4937669343898</t>
+          <t>-707.6478495252077</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-966.4036782923813</t>
+          <t>-1032.995303774706</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5442.0</t>
+          <t>3050.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1615,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1625,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1717,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-2.16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-38.91</t>
+          <t>-27.28</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-36.69</t>
+          <t>-37.10</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.97</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
+          <t>93.33</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>2.53</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-4.68</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>37.67</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>36.55</v>
+        <v>36.74</v>
       </c>
       <c r="AN4" t="n">
         <v>36.38</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>38.06</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>63.23</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
+          <t>47.16</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.34</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-80.83</t>
+          <t>-78.27</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4189.0</t>
+          <t>5442.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3761.6</v>
+        <v>4414.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>6157.4</t>
+          <t>6070.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>9610.879999999999</v>
+        <v>9569.120000000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2395</t>
+          <t>-1655</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-590.6919648693004</t>
+          <t>-648.4937669343898</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1093.044081950046</t>
+          <t>-966.4036782923813</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4189.0</t>
+          <t>5442.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>38.5</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>37.95</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>38.05</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>110.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-50.78</t>
+          <t>-38.91</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-36.69</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,33 +2259,33 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,59 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.73</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2.71</t>
-        </is>
+          <t>96.97</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2.68</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-4.68</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>37.36</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>36.37</v>
+        <v>36.55</v>
       </c>
       <c r="AN5" t="n">
         <v>36.38</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>75.65</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
+          <t>63.23</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.3</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-83.86</t>
+          <t>-80.83</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4678.0</t>
+          <t>4189.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3549.2</v>
+        <v>3761.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>7210.5</t>
+          <t>6157.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>9780.68</v>
+        <v>9610.879999999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-3661</t>
+          <t>-2395</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-499.3552163091647</t>
+          <t>-590.6919648693004</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1100.671655677066</t>
+          <t>-1093.044081950046</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4678.0</t>
+          <t>4189.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>38.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>37.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>38.05</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-48.33</t>
+          <t>-50.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-37.44</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>54.55</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>2.86</t>
-        </is>
+          <t>72.73</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2.71</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.36</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>36.18</v>
+        <v>36.37</v>
       </c>
       <c r="AN6" t="n">
         <v>36.38</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>38.37</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>87.23</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.21</t>
-        </is>
+          <t>75.65</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.26</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>-83.86</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3849.8</v>
+        <v>3549.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>7451.1</t>
+          <t>7210.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>9807.120000000001</v>
+        <v>9780.68</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-3601</t>
+          <t>-3661</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-390.0249546059099</t>
+          <t>-499.3552163091647</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1124.651344727199</t>
+          <t>-1100.671655677066</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5403.0</t>
+          <t>4678.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-38.22</t>
+          <t>-48.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-38.60</t>
+          <t>-37.44</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,74 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>42.42</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>-0.43</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+          <t>54.55</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.86</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.19</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>36.03</v>
+        <v>36.18</v>
       </c>
       <c r="AN7" t="n">
-        <v>36.4</v>
+        <v>36.38</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>38.37</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>113.09</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
+          <t>87.23</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.21</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-89.77</t>
+          <t>-86.91</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>5058.2</v>
+        <v>3849.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>8187.9</t>
+          <t>7451.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>9806.860000000001</v>
+        <v>9807.120000000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-3129</t>
+          <t>-3601</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-256.4565200384027</t>
+          <t>-390.0249546059099</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1196.420495344275</t>
+          <t>-1124.651344727199</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2359.0</t>
+          <t>5403.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>36.85</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-14.53</t>
+          <t>-38.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-38.27</t>
+          <t>-38.60</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>58.82</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>3.68</t>
-        </is>
+          <t>42.42</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>2.85</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-5.42</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>37.22</t>
+          <t>37.06</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>35.9</v>
+        <v>36.03</v>
       </c>
       <c r="AN8" t="n">
-        <v>36.42</v>
+        <v>36.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>207.15</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
+          <t>113.09</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.16</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-92.66</t>
+          <t>-89.77</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>7725.8</v>
+        <v>5058.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>9038.7</t>
+          <t>8187.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>10088.66</v>
+        <v>9806.860000000001</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1312</t>
+          <t>-3129</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-85.55397907369867</t>
+          <t>-256.4565200384027</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-930.0756928206583</t>
+          <t>-1196.420495344275</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2179.0</t>
+          <t>2359.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3796,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>37.25</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>36.85</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3898,7 +3842,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-10.90</t>
+          <t>-14.53</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-38.10</t>
+          <t>-38.27</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>62.72</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
+          <t>58.82</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>3.68</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>37.22000000000001</t>
+          <t>37.22</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>35.77</v>
+        <v>35.9</v>
       </c>
       <c r="AN9" t="n">
-        <v>36.45</v>
+        <v>36.42</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>518.15</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
+          <t>207.15</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.12</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-96.46</t>
+          <t>-92.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>8553.200000000001</v>
+        <v>7725.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>9599.8</t>
+          <t>9038.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>10349.7</v>
+        <v>10088.66</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1046</t>
+          <t>-1312</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>67.99542342574854</t>
+          <t>-85.55397907369867</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-497.0804144718968</t>
+          <t>-930.0756928206583</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3127.0</t>
+          <t>2179.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,12 +4212,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.25</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4291,7 +4227,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.80</t>
+          <t>-10.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-37.94</t>
+          <t>-38.10</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,74 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>76.47</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>77.87</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
+          <t>62.72</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>4.05</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.32</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-5.93</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.22000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>35.64</v>
+        <v>35.77</v>
       </c>
       <c r="AN10" t="n">
-        <v>36.49</v>
+        <v>36.45</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.79</t>
+          <t>38.69</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2018.96</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
+          <t>518.15</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.06</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4530,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.05</t>
+          <t>-96.46</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>10871.8</v>
+        <v>8553.200000000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>9992.1</t>
+          <t>9599.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>10687.76</v>
+        <v>10349.7</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>879</t>
+          <t>-1046</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>170.7364848616841</t>
+          <t>67.99542342574854</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>37.6657122574743</t>
+          <t>-497.0804144718968</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>6181.0</t>
+          <t>3127.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4656,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4634,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>310.0</t>
+          <t>165.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-9.31</t>
+          <t>8.80</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-38.77</t>
+          <t>-37.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>76.47</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>85.71</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-0.67</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+          <t>77.87</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>4.09</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.32</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-6.06</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>37.05</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>35.51</v>
+        <v>35.64</v>
       </c>
       <c r="AN11" t="n">
-        <v>36.53</v>
+        <v>36.49</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>38.79</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>365.87</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
+          <t>2018.96</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0.02</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-106.32</t>
+          <t>-101.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>11052.4</v>
+        <v>10871.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12187.3</t>
+          <t>9992.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>10895.12</v>
+        <v>10687.76</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1134</t>
+          <t>879</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>194.9311707897222</t>
+          <t>170.7364848616841</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>473.0292607188057</t>
+          <t>37.6657122574743</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>11445.0</t>
+          <t>6181.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-1.97</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>37.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d1】;【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>414.0</t>
+          <t>310.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-6.20</t>
+          <t>-9.31</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.77</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,74 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>139</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>95.52</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>4.71</t>
-        </is>
+          <t>85.71</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>4.33</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.06</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>37.06</t>
+          <t>37.05</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>35.39</v>
+        <v>35.51</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.59</v>
+        <v>36.53</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>229.08</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.19</t>
-        </is>
+          <t>365.87</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0.1</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.10</t>
+          <t>-106.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>30366.92553191489</t>
+          <t>30334.90580736544</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>11317.6</v>
+        <v>11052.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12066.3</t>
+          <t>12187.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>11140.44</v>
+        <v>10895.12</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-748</t>
+          <t>-1134</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>144.367881711707</t>
+          <t>194.9311707897222</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>514.0832849236103</t>
+          <t>473.0292607188057</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>15697.0</t>
+          <t>11445.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.38</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.34</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5601,11 +5513,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>1809</t>
@@ -5613,12 +5521,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>321.293</t>
+          <t>164.543</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5536,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5551,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-10.61</t>
+          <t>-12.51</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5621,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5631,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,74 +5652,66 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>84.72</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-0.77</t>
-        </is>
+          <t>80.75</t>
+        </is>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>-1.01</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-2.96</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AM13" t="n">
         <v>18.07</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.66</v>
+        <v>18.62</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>19.07</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>17.25</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.26</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5820,7 +5720,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-106.93</t>
+          <t>-106.63</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5730,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>68331381.42978723</t>
+          <t>68240841.18059489</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>5737884.0</t>
+          <t>2939977.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>7061273.6</v>
+        <v>6173528.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7899374.7</t>
+          <t>7056660.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>25505500.48</v>
+        <v>25243963.02</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-838101</t>
+          <t>-883131</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-2712874.864740888</t>
+          <t>-2808378.556643823</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3259262.554683162</t>
+          <t>-3333648.862109963</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>5737884.0</t>
+          <t>2939977.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5786,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5831,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5946,7 +5846,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5856,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>105.59</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5871,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>144.36</t>
+          <t>142.92</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,12 +5896,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6011,7 +5911,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>17.95</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6031,11 +5931,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>1809</t>
@@ -6043,12 +5939,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>494.137</t>
+          <t>321.293</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +5954,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +5964,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-12.58</t>
+          <t>-10.61</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6039,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6049,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,274 +6070,266 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>81.48</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-0.72</t>
-        </is>
+          <t>84.72</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0.77</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
+          <t>17.93</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>19.05</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>17.25</t>
+        </is>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>3.98</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-106.93</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>68240841.18059489</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>5737884.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>7061273.6</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>7899374.7</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>25505500.48</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-838101</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-2712874.864740888</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-3259262.554683162</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>5737884.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>16.15</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/08/07</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>11.15</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>中釉</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>中釉</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>4.154975628533399</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>16.21035637221673</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>6.111603549217973</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>18.68%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>142.92</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>2982</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>色釉料76.73%、其他19.26%、玉晶石4.01% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>中釉-玻璃陶瓷-上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>玻璃陶瓷平上市</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
           <t>17.95</t>
         </is>
       </c>
-      <c r="AM14" t="n">
-        <v>18.08</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>18.68</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>19.03</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>13.40</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-0.25</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-107.23</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>68331381.42978723</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>8912758.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>7286683.2</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>8335142.1</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>25916531.72</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-1048458</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-2613531.648387747</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-3336369.917120475</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>8912758.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>16.15</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/08/07</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>10.84</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>中釉</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>中釉</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>4.154975628533399</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>16.21035637221673</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>6.111603549217973</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>105.59</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>18.68%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>-0.05%</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>144.36</t>
-        </is>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>2998</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>色釉料76.73%、其他19.26%、玉晶石4.01% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>中釉-玻璃陶瓷-上市</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>玻璃陶瓷平上市</t>
-        </is>
-      </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>18.15</t>
-        </is>
-      </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6461,11 +6349,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>1809</t>
@@ -6473,12 +6357,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>361.704</t>
+          <t>494.137</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6382,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-12.58</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6467,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6488,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,27 +6503,23 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>87.04</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
+          <t>81.48</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.72</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -6651,27 +6531,23 @@
         <v>18.08</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.72</v>
+        <v>18.68</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>19.01</t>
+          <t>19.03</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>10.16</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
+          <t>13.40</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0.29</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6680,7 +6556,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-107.47</t>
+          <t>-107.23</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6566,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>68331381.42978723</t>
+          <t>68240841.18059489</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>6511141.0</t>
+          <t>8912758.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>8405984.800000001</v>
+        <v>7286683.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8330496.4</t>
+          <t>8335142.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>26697893.5</v>
+        <v>25916531.72</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>-1048458</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-2482106.508618161</t>
+          <t>-2613531.648387747</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3667532.294990905</t>
+          <t>-3336369.917120475</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>6511141.0</t>
+          <t>8912758.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6806,7 +6682,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6692,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>105.59</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6707,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>144.36</t>
+          <t>142.92</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,7 +6732,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -6866,7 +6742,7 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6891,11 +6767,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>1809</t>
@@ -6903,12 +6775,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>377.614</t>
+          <t>361.704</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6790,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6800,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-12.27</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +6875,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +6885,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,74 +6906,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>87.83</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-1.31</t>
-        </is>
+          <t>87.04</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0.71</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>17.84</t>
+          <t>17.95</t>
         </is>
       </c>
       <c r="AM16" t="n">
         <v>18.08</v>
       </c>
       <c r="AN16" t="n">
-        <v>18.75</v>
+        <v>18.72</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18.99</t>
+          <t>19.01</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>6.12</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-0.29</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
+          <t>10.16</t>
+        </is>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -7110,7 +6974,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-107.66</t>
+          <t>-107.47</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +6984,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>68331381.42978723</t>
+          <t>68240841.18059489</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>6765882.0</t>
+          <t>6511141.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>8347899.8</v>
+        <v>8405984.800000001</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>9515210.0</t>
+          <t>8330496.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>27422411.38</v>
+        <v>26697893.5</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1167310</t>
+          <t>75488</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-2266574.54745948</t>
+          <t>-2482106.508618161</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3752322.002841841</t>
+          <t>-3667532.294990905</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>6765882.0</t>
+          <t>6511141.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7040,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>10.53</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7085,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7236,7 +7100,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7110,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>105.59</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7125,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>144.36</t>
+          <t>142.92</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,7 +7150,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7296,12 +7160,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7321,11 +7185,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>【d】</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>1809</t>
@@ -7333,42 +7193,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>377.614</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>17.85</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>406.71</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>18.05</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-26.72</t>
+          <t>-12.27</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7293,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7303,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,74 +7324,66 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>74.73</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-2.21</t>
-        </is>
+          <t>87.83</t>
+        </is>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>-1.31</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>17.84</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>18.12</v>
+        <v>18.08</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.78</v>
+        <v>18.75</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>18.97</t>
+          <t>18.99</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>2.66</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
+          <t>6.12</t>
+        </is>
+      </c>
+      <c r="AQ17" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>-0.3</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7540,7 +7392,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-107.78</t>
+          <t>-107.66</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7402,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>68331381.42978723</t>
+          <t>68240841.18059489</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>7939791.6</v>
+        <v>8347899.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10834811.3</t>
+          <t>9515210.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>27808635.82</v>
+        <v>27422411.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2895019</t>
+          <t>-1167310</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-1996438.646480869</t>
+          <t>-2266574.54745948</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3766732.335384544</t>
+          <t>-3752322.002841841</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>7378703.0</t>
+          <t>6765882.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7458,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7503,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7513,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7528,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>105.59</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7543,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>144.36</t>
+          <t>142.92</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7568,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>18.3</t>
+          <t>18.15</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7751,11 +7603,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>1809</t>
@@ -7763,12 +7611,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>381.935</t>
+          <t>406.71</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,17 +7636,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-36.77</t>
+          <t>-26.72</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7721,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,74 +7742,66 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>43.73</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-3.28</t>
-        </is>
+          <t>74.73</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>-2.21</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>17.54</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>18.14</v>
+        <v>18.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>18.82</v>
+        <v>18.78</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.97</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-8.02</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>-0.31</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7970,7 +7810,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-107.83</t>
+          <t>-107.78</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7820,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>68331381.42978723</t>
+          <t>68240841.18059489</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>8737475.800000001</v>
+        <v>7939791.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>13819369.0</t>
+          <t>10834811.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>28136264.12</v>
+        <v>27808635.82</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-5081893</t>
+          <t>-2895019</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-1674567.0666802</t>
+          <t>-1996438.646480869</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3718451.762753243</t>
+          <t>-3766732.335384544</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>6864932.0</t>
+          <t>7378703.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8081,7 +7921,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8096,7 +7936,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +7946,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>105.59</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +7961,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>144.36</t>
+          <t>142.92</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8156,7 +7996,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>17.75</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8033,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>811.45</t>
+          <t>381.935</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8048,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8058,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-59.12</t>
+          <t>-36.77</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8133,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-5.04</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8143,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,74 +8164,66 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>16.33</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-3.47</t>
-        </is>
+          <t>43.73</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>-3.28</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>17.52</t>
+          <t>17.54</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>18.15</v>
+        <v>18.14</v>
       </c>
       <c r="AN19" t="n">
-        <v>18.86</v>
+        <v>18.82</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>18.93</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-23.36</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.31</t>
-        </is>
+          <t>-8.02</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>-0.31</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8400,7 +8232,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-107.67</t>
+          <t>-107.83</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8242,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>68331381.42978723</t>
+          <t>68240841.18059489</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>9383601</v>
+        <v>8737475.800000001</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>22951484.1</t>
+          <t>13819369.0</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>28459246.14</v>
+        <v>28136264.12</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-13567883</t>
+          <t>-5081893</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-1302951.667394193</t>
+          <t>-1674567.0666802</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3461630.774610199</t>
+          <t>-3718451.762753243</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>14509266.0</t>
+          <t>6864932.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8298,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8343,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8368,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>105.59</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8383,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>144.36</t>
+          <t>142.92</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>2998</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8408,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.05</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>18.3</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>17.75</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
           <t>18.05</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>17.5</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>17.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8455,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>356.458</t>
+          <t>811.45</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8470,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8480,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-74.28</t>
+          <t>-59.12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8555,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-7.96</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8565,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>5.73</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,74 +8586,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>165</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>3.51</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
+          <t>16.33</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
         <is>
           <t>-0.40</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-4.26</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>-3.65</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>-0.14</t>
-        </is>
-      </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>17.52</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>18.2</v>
+        <v>18.15</v>
       </c>
       <c r="AN20" t="n">
-        <v>18.89</v>
+        <v>18.86</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>18.91</t>
+          <t>18.93</t>
         </is>
       </c>
 